--- a/cuadros/ABRIL/Abril_Acasias_villas.xlsx
+++ b/cuadros/ABRIL/Abril_Acasias_villas.xlsx
@@ -1,22 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\KC\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CFBF95B-0A3D-408E-B05B-CFF1270A2E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="14133" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23256" windowHeight="13176"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="REFERENCIA" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
@@ -523,9 +517,6 @@
     <t>NRO DE CONTROL ERRADO, NRO CORRECTO: 11358</t>
   </si>
   <si>
-    <t>00069980 / 00069978</t>
-  </si>
-  <si>
     <t>00069298</t>
   </si>
   <si>
@@ -617,12 +608,15 @@
   </si>
   <si>
     <t>00056918</t>
+  </si>
+  <si>
+    <t>00069980</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1143,9 +1137,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K500"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.9375" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -1159,7 +1153,7 @@
     <col min="11" max="11" width="12" style="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1194,7 +1188,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
@@ -1225,9 +1219,9 @@
       </c>
       <c r="J2" s="9"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>35</v>
@@ -1258,12 +1252,12 @@
         <v>114</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="26" x14ac:dyDescent="0.5">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>38</v>
@@ -1292,7 +1286,7 @@
       </c>
       <c r="J4" s="9"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>31</v>
       </c>
@@ -1320,7 +1314,7 @@
       </c>
       <c r="J5" s="9"/>
     </row>
-    <row r="6" spans="1:11" ht="78" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:11" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>31</v>
       </c>
@@ -1353,9 +1347,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>46</v>
@@ -1384,9 +1378,9 @@
       </c>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:11" ht="26" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>48</v>
@@ -1417,9 +1411,9 @@
         <v>426</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="26" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>51</v>
@@ -1448,9 +1442,9 @@
       </c>
       <c r="J9" s="9"/>
     </row>
-    <row r="10" spans="1:11" ht="26" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>54</v>
@@ -1481,12 +1475,12 @@
         <v>123</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="26" x14ac:dyDescent="0.5">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>54</v>
@@ -1517,12 +1511,12 @@
         <v>125</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="26" x14ac:dyDescent="0.5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>58</v>
@@ -1551,7 +1545,7 @@
       </c>
       <c r="J12" s="9"/>
     </row>
-    <row r="13" spans="1:11" ht="26" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>31</v>
       </c>
@@ -1582,7 +1576,7 @@
       </c>
       <c r="J13" s="9"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>31</v>
       </c>
@@ -1613,9 +1607,9 @@
       </c>
       <c r="J14" s="9"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>64</v>
@@ -1644,7 +1638,7 @@
       </c>
       <c r="J15" s="9"/>
     </row>
-    <row r="16" spans="1:11" ht="26" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>31</v>
       </c>
@@ -1677,7 +1671,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="26" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>31</v>
       </c>
@@ -1708,9 +1702,9 @@
       </c>
       <c r="J17" s="9"/>
     </row>
-    <row r="18" spans="1:11" ht="39" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>70</v>
@@ -1739,7 +1733,7 @@
       </c>
       <c r="J18" s="9"/>
     </row>
-    <row r="19" spans="1:11" ht="26" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>31</v>
       </c>
@@ -1770,7 +1764,7 @@
       </c>
       <c r="J19" s="9"/>
     </row>
-    <row r="20" spans="1:11" ht="26" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>31</v>
       </c>
@@ -1801,7 +1795,7 @@
       </c>
       <c r="J20" s="9"/>
     </row>
-    <row r="21" spans="1:11" ht="26" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>31</v>
       </c>
@@ -1832,7 +1826,7 @@
       </c>
       <c r="J21" s="9"/>
     </row>
-    <row r="22" spans="1:11" ht="26" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>31</v>
       </c>
@@ -1865,12 +1859,12 @@
         <v>0.4</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.5">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>32</v>
@@ -1901,12 +1895,12 @@
         <v>138</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.5">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>80</v>
@@ -1935,9 +1929,9 @@
       </c>
       <c r="J24" s="9"/>
     </row>
-    <row r="25" spans="1:11" ht="26" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>54</v>
@@ -1966,7 +1960,7 @@
       </c>
       <c r="J25" s="9"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>31</v>
       </c>
@@ -1997,9 +1991,9 @@
       </c>
       <c r="J26" s="9"/>
     </row>
-    <row r="27" spans="1:11" ht="26" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>85</v>
@@ -2028,7 +2022,7 @@
       </c>
       <c r="J27" s="9"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>31</v>
       </c>
@@ -2059,9 +2053,9 @@
       </c>
       <c r="J28" s="9"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>86</v>
@@ -2090,9 +2084,9 @@
       </c>
       <c r="J29" s="9"/>
     </row>
-    <row r="30" spans="1:11" ht="26" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>88</v>
@@ -2121,9 +2115,9 @@
       </c>
       <c r="J30" s="9"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>32</v>
@@ -2152,9 +2146,9 @@
       </c>
       <c r="J31" s="9"/>
     </row>
-    <row r="32" spans="1:11" ht="26" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>90</v>
@@ -2183,7 +2177,7 @@
       </c>
       <c r="J32" s="9"/>
     </row>
-    <row r="33" spans="1:11" ht="52" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:11" ht="69" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>31</v>
       </c>
@@ -2216,7 +2210,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="26" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>31</v>
       </c>
@@ -2249,12 +2243,12 @@
         <v>151</v>
       </c>
       <c r="K34" s="13" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="28.7" x14ac:dyDescent="0.5">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>32</v>
@@ -2285,12 +2279,12 @@
         <v>153</v>
       </c>
       <c r="K35" s="20" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="26" x14ac:dyDescent="0.5">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>96</v>
@@ -2319,9 +2313,9 @@
       </c>
       <c r="J36" s="9"/>
     </row>
-    <row r="37" spans="1:11" ht="26" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>98</v>
@@ -2352,12 +2346,12 @@
         <v>12.34</v>
       </c>
       <c r="K37" s="13" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="26" x14ac:dyDescent="0.5">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>66</v>
@@ -2388,9 +2382,9 @@
         <v>124.3</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="26" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>54</v>
@@ -2421,12 +2415,12 @@
         <v>3.35</v>
       </c>
       <c r="K39" s="13" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="28.7" x14ac:dyDescent="0.5">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>80</v>
@@ -2455,7 +2449,7 @@
       </c>
       <c r="J40" s="17"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>31</v>
       </c>
@@ -2485,7 +2479,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>31</v>
       </c>
@@ -2515,9 +2509,9 @@
         <v>160</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>80</v>
@@ -2545,7 +2539,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="22.7" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>31</v>
       </c>
@@ -2575,9 +2569,9 @@
         <v>162</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>108</v>
@@ -2605,7 +2599,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="25.35" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>31</v>
       </c>
@@ -2635,15 +2629,15 @@
         <v>164</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D47" s="5">
         <v>46142</v>
@@ -2662,18 +2656,18 @@
         <v>TIPO A</v>
       </c>
       <c r="I47" s="18" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.5">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D48" s="5">
         <v>46142</v>
@@ -2692,18 +2686,18 @@
         <v>TIPO A</v>
       </c>
       <c r="I48" s="18" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.5">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="24" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B49" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="C49" s="13" t="s">
         <v>180</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>181</v>
       </c>
       <c r="D49" s="5">
         <v>46142</v>
@@ -2722,10 +2716,10 @@
         <v>TIPO B</v>
       </c>
       <c r="I49" s="18" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="26" x14ac:dyDescent="0.5">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>31</v>
       </c>
@@ -2733,7 +2727,7 @@
         <v>76</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D50" s="5">
         <v>46142</v>
@@ -2752,18 +2746,18 @@
         <v>TIPO A</v>
       </c>
       <c r="I50" s="18" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.5">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D51" s="5">
         <v>46142</v>
@@ -2782,18 +2776,18 @@
         <v>TIPO A</v>
       </c>
       <c r="I51" s="18" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.5">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D52" s="5">
         <v>46142</v>
@@ -2812,18 +2806,18 @@
         <v>TIPO A</v>
       </c>
       <c r="I52" s="18" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="52.35" x14ac:dyDescent="0.5">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="69" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B53" t="s">
+        <v>192</v>
+      </c>
+      <c r="C53" s="13" t="s">
         <v>193</v>
-      </c>
-      <c r="C53" s="13" t="s">
-        <v>194</v>
       </c>
       <c r="D53" s="5">
         <v>46142</v>
@@ -2842,21 +2836,21 @@
         <v>TIPO E</v>
       </c>
       <c r="I53" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J53" s="25">
         <v>380.82</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B54" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D54" s="5">
         <v>46142</v>
@@ -2875,2686 +2869,2686 @@
         <v>TIPO D</v>
       </c>
       <c r="I54" s="18" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J54" s="23">
         <v>0.65</v>
       </c>
       <c r="K54" s="13" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.5">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H55" t="str">
         <f>IF(G55="","",VLOOKUP(G55,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H56" t="str">
         <f>IF(G56="","",VLOOKUP(G56,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H57" t="str">
         <f>IF(G57="","",VLOOKUP(G57,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H58" t="str">
         <f>IF(G58="","",VLOOKUP(G58,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H59" t="str">
         <f>IF(G59="","",VLOOKUP(G59,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H60" t="str">
         <f>IF(G60="","",VLOOKUP(G60,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H61" t="str">
         <f>IF(G61="","",VLOOKUP(G61,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H62" t="str">
         <f>IF(G62="","",VLOOKUP(G62,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H63" t="str">
         <f>IF(G63="","",VLOOKUP(G63,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H64" t="str">
         <f>IF(G64="","",VLOOKUP(G64,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="65" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="65" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H65" t="str">
         <f>IF(G65="","",VLOOKUP(G65,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="66" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="66" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H66" t="str">
         <f>IF(G66="","",VLOOKUP(G66,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="67" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="67" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H67" t="str">
         <f>IF(G67="","",VLOOKUP(G67,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="68" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="68" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H68" t="str">
         <f>IF(G68="","",VLOOKUP(G68,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="69" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="69" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H69" t="str">
         <f>IF(G69="","",VLOOKUP(G69,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="70" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="70" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H70" t="str">
         <f>IF(G70="","",VLOOKUP(G70,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="71" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="71" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H71" t="str">
         <f>IF(G71="","",VLOOKUP(G71,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="72" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="72" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H72" t="str">
         <f>IF(G72="","",VLOOKUP(G72,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="73" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="73" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H73" t="str">
         <f>IF(G73="","",VLOOKUP(G73,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="74" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="74" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H74" t="str">
         <f>IF(G74="","",VLOOKUP(G74,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="75" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="75" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H75" t="str">
         <f>IF(G75="","",VLOOKUP(G75,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="76" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="76" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H76" t="str">
         <f>IF(G76="","",VLOOKUP(G76,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="77" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="77" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H77" t="str">
         <f>IF(G77="","",VLOOKUP(G77,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="78" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="78" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H78" t="str">
         <f>IF(G78="","",VLOOKUP(G78,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="79" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="79" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H79" t="str">
         <f>IF(G79="","",VLOOKUP(G79,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="80" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="80" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H80" t="str">
         <f>IF(G80="","",VLOOKUP(G80,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="81" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="81" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H81" t="str">
         <f>IF(G81="","",VLOOKUP(G81,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="82" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="82" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H82" t="str">
         <f>IF(G82="","",VLOOKUP(G82,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="83" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="83" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H83" t="str">
         <f>IF(G83="","",VLOOKUP(G83,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="84" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="84" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H84" t="str">
         <f>IF(G84="","",VLOOKUP(G84,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="85" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="85" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H85" t="str">
         <f>IF(G85="","",VLOOKUP(G85,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="86" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="86" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H86" t="str">
         <f>IF(G86="","",VLOOKUP(G86,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="87" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="87" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H87" t="str">
         <f>IF(G87="","",VLOOKUP(G87,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="88" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="88" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H88" t="str">
         <f>IF(G88="","",VLOOKUP(G88,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="89" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="89" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H89" t="str">
         <f>IF(G89="","",VLOOKUP(G89,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="90" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="90" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H90" t="str">
         <f>IF(G90="","",VLOOKUP(G90,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="91" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="91" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H91" t="str">
         <f>IF(G91="","",VLOOKUP(G91,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="92" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="92" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H92" t="str">
         <f>IF(G92="","",VLOOKUP(G92,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="93" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="93" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H93" t="str">
         <f>IF(G93="","",VLOOKUP(G93,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="94" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="94" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H94" t="str">
         <f>IF(G94="","",VLOOKUP(G94,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="95" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="95" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H95" t="str">
         <f>IF(G95="","",VLOOKUP(G95,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="96" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="96" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H96" t="str">
         <f>IF(G96="","",VLOOKUP(G96,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="97" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="97" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H97" t="str">
         <f>IF(G97="","",VLOOKUP(G97,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="98" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="98" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H98" t="str">
         <f>IF(G98="","",VLOOKUP(G98,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="99" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="99" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H99" t="str">
         <f>IF(G99="","",VLOOKUP(G99,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="100" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="100" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H100" t="str">
         <f>IF(G100="","",VLOOKUP(G100,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="101" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="101" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H101" t="str">
         <f>IF(G101="","",VLOOKUP(G101,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="102" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="102" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H102" t="str">
         <f>IF(G102="","",VLOOKUP(G102,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="103" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="103" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H103" t="str">
         <f>IF(G103="","",VLOOKUP(G103,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="104" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="104" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H104" t="str">
         <f>IF(G104="","",VLOOKUP(G104,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="105" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="105" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H105" t="str">
         <f>IF(G105="","",VLOOKUP(G105,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="106" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="106" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H106" t="str">
         <f>IF(G106="","",VLOOKUP(G106,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="107" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="107" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H107" t="str">
         <f>IF(G107="","",VLOOKUP(G107,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="108" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="108" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H108" t="str">
         <f>IF(G108="","",VLOOKUP(G108,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="109" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="109" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H109" t="str">
         <f>IF(G109="","",VLOOKUP(G109,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="110" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="110" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H110" t="str">
         <f>IF(G110="","",VLOOKUP(G110,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="111" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="111" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H111" t="str">
         <f>IF(G111="","",VLOOKUP(G111,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="112" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="112" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H112" t="str">
         <f>IF(G112="","",VLOOKUP(G112,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="113" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="113" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H113" t="str">
         <f>IF(G113="","",VLOOKUP(G113,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="114" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="114" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H114" t="str">
         <f>IF(G114="","",VLOOKUP(G114,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="115" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="115" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H115" t="str">
         <f>IF(G115="","",VLOOKUP(G115,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="116" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="116" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H116" t="str">
         <f>IF(G116="","",VLOOKUP(G116,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="117" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="117" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H117" t="str">
         <f>IF(G117="","",VLOOKUP(G117,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="118" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="118" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H118" t="str">
         <f>IF(G118="","",VLOOKUP(G118,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="119" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="119" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H119" t="str">
         <f>IF(G119="","",VLOOKUP(G119,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="120" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="120" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H120" t="str">
         <f>IF(G120="","",VLOOKUP(G120,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="121" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="121" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H121" t="str">
         <f>IF(G121="","",VLOOKUP(G121,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="122" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="122" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H122" t="str">
         <f>IF(G122="","",VLOOKUP(G122,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="123" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="123" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H123" t="str">
         <f>IF(G123="","",VLOOKUP(G123,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="124" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="124" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H124" t="str">
         <f>IF(G124="","",VLOOKUP(G124,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="125" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="125" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H125" t="str">
         <f>IF(G125="","",VLOOKUP(G125,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="126" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H126" t="str">
         <f>IF(G126="","",VLOOKUP(G126,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="127" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H127" t="str">
         <f>IF(G127="","",VLOOKUP(G127,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="128" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="128" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H128" t="str">
         <f>IF(G128="","",VLOOKUP(G128,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="129" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="129" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H129" t="str">
         <f>IF(G129="","",VLOOKUP(G129,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="130" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="130" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H130" t="str">
         <f>IF(G130="","",VLOOKUP(G130,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="131" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="131" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H131" t="str">
         <f>IF(G131="","",VLOOKUP(G131,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="132" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="132" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H132" t="str">
         <f>IF(G132="","",VLOOKUP(G132,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="133" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="133" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H133" t="str">
         <f>IF(G133="","",VLOOKUP(G133,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="134" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="134" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H134" t="str">
         <f>IF(G134="","",VLOOKUP(G134,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="135" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="135" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H135" t="str">
         <f>IF(G135="","",VLOOKUP(G135,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="136" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="136" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H136" t="str">
         <f>IF(G136="","",VLOOKUP(G136,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="137" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="137" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H137" t="str">
         <f>IF(G137="","",VLOOKUP(G137,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="138" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="138" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H138" t="str">
         <f>IF(G138="","",VLOOKUP(G138,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="139" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="139" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H139" t="str">
         <f>IF(G139="","",VLOOKUP(G139,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="140" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="140" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H140" t="str">
         <f>IF(G140="","",VLOOKUP(G140,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="141" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="141" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H141" t="str">
         <f>IF(G141="","",VLOOKUP(G141,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="142" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="142" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H142" t="str">
         <f>IF(G142="","",VLOOKUP(G142,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="143" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="143" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H143" t="str">
         <f>IF(G143="","",VLOOKUP(G143,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="144" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="144" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H144" t="str">
         <f>IF(G144="","",VLOOKUP(G144,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="145" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="145" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H145" t="str">
         <f>IF(G145="","",VLOOKUP(G145,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="146" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="146" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H146" t="str">
         <f>IF(G146="","",VLOOKUP(G146,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="147" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="147" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H147" t="str">
         <f>IF(G147="","",VLOOKUP(G147,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="148" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="148" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H148" t="str">
         <f>IF(G148="","",VLOOKUP(G148,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="149" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="149" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H149" t="str">
         <f>IF(G149="","",VLOOKUP(G149,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="150" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="150" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H150" t="str">
         <f>IF(G150="","",VLOOKUP(G150,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="151" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="151" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H151" t="str">
         <f>IF(G151="","",VLOOKUP(G151,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="152" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="152" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H152" t="str">
         <f>IF(G152="","",VLOOKUP(G152,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="153" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="153" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H153" t="str">
         <f>IF(G153="","",VLOOKUP(G153,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="154" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="154" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H154" t="str">
         <f>IF(G154="","",VLOOKUP(G154,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="155" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="155" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H155" t="str">
         <f>IF(G155="","",VLOOKUP(G155,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="156" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="156" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H156" t="str">
         <f>IF(G156="","",VLOOKUP(G156,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="157" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="157" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H157" t="str">
         <f>IF(G157="","",VLOOKUP(G157,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="158" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="158" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H158" t="str">
         <f>IF(G158="","",VLOOKUP(G158,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="159" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="159" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H159" t="str">
         <f>IF(G159="","",VLOOKUP(G159,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="160" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="160" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H160" t="str">
         <f>IF(G160="","",VLOOKUP(G160,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="161" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="161" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H161" t="str">
         <f>IF(G161="","",VLOOKUP(G161,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="162" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="162" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H162" t="str">
         <f>IF(G162="","",VLOOKUP(G162,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="163" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="163" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H163" t="str">
         <f>IF(G163="","",VLOOKUP(G163,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="164" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="164" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H164" t="str">
         <f>IF(G164="","",VLOOKUP(G164,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="165" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="165" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H165" t="str">
         <f>IF(G165="","",VLOOKUP(G165,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="166" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="166" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H166" t="str">
         <f>IF(G166="","",VLOOKUP(G166,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="167" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="167" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H167" t="str">
         <f>IF(G167="","",VLOOKUP(G167,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="168" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="168" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H168" t="str">
         <f>IF(G168="","",VLOOKUP(G168,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="169" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="169" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H169" t="str">
         <f>IF(G169="","",VLOOKUP(G169,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="170" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="170" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H170" t="str">
         <f>IF(G170="","",VLOOKUP(G170,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="171" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="171" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H171" t="str">
         <f>IF(G171="","",VLOOKUP(G171,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="172" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="172" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H172" t="str">
         <f>IF(G172="","",VLOOKUP(G172,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="173" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="173" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H173" t="str">
         <f>IF(G173="","",VLOOKUP(G173,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="174" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="174" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H174" t="str">
         <f>IF(G174="","",VLOOKUP(G174,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="175" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="175" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H175" t="str">
         <f>IF(G175="","",VLOOKUP(G175,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="176" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="176" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H176" t="str">
         <f>IF(G176="","",VLOOKUP(G176,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="177" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="177" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H177" t="str">
         <f>IF(G177="","",VLOOKUP(G177,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="178" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="178" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H178" t="str">
         <f>IF(G178="","",VLOOKUP(G178,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="179" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="179" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H179" t="str">
         <f>IF(G179="","",VLOOKUP(G179,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="180" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="180" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H180" t="str">
         <f>IF(G180="","",VLOOKUP(G180,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="181" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="181" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H181" t="str">
         <f>IF(G181="","",VLOOKUP(G181,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="182" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="182" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H182" t="str">
         <f>IF(G182="","",VLOOKUP(G182,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="183" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="183" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H183" t="str">
         <f>IF(G183="","",VLOOKUP(G183,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="184" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="184" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H184" t="str">
         <f>IF(G184="","",VLOOKUP(G184,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="185" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="185" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H185" t="str">
         <f>IF(G185="","",VLOOKUP(G185,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="186" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="186" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H186" t="str">
         <f>IF(G186="","",VLOOKUP(G186,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="187" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="187" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H187" t="str">
         <f>IF(G187="","",VLOOKUP(G187,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="188" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="188" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H188" t="str">
         <f>IF(G188="","",VLOOKUP(G188,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="189" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="189" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H189" t="str">
         <f>IF(G189="","",VLOOKUP(G189,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="190" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="190" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H190" t="str">
         <f>IF(G190="","",VLOOKUP(G190,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="191" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="191" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H191" t="str">
         <f>IF(G191="","",VLOOKUP(G191,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="192" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="192" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H192" t="str">
         <f>IF(G192="","",VLOOKUP(G192,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="193" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="193" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H193" t="str">
         <f>IF(G193="","",VLOOKUP(G193,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="194" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="194" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H194" t="str">
         <f>IF(G194="","",VLOOKUP(G194,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="195" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="195" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H195" t="str">
         <f>IF(G195="","",VLOOKUP(G195,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="196" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="196" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H196" t="str">
         <f>IF(G196="","",VLOOKUP(G196,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="197" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="197" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H197" t="str">
         <f>IF(G197="","",VLOOKUP(G197,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="198" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="198" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H198" t="str">
         <f>IF(G198="","",VLOOKUP(G198,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="199" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="199" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H199" t="str">
         <f>IF(G199="","",VLOOKUP(G199,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="200" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="200" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H200" t="str">
         <f>IF(G200="","",VLOOKUP(G200,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="201" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="201" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H201" t="str">
         <f>IF(G201="","",VLOOKUP(G201,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="202" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="202" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H202" t="str">
         <f>IF(G202="","",VLOOKUP(G202,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="203" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="203" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H203" t="str">
         <f>IF(G203="","",VLOOKUP(G203,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="204" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="204" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H204" t="str">
         <f>IF(G204="","",VLOOKUP(G204,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="205" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="205" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H205" t="str">
         <f>IF(G205="","",VLOOKUP(G205,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="206" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="206" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H206" t="str">
         <f>IF(G206="","",VLOOKUP(G206,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="207" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="207" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H207" t="str">
         <f>IF(G207="","",VLOOKUP(G207,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="208" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="208" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H208" t="str">
         <f>IF(G208="","",VLOOKUP(G208,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="209" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="209" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H209" t="str">
         <f>IF(G209="","",VLOOKUP(G209,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="210" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="210" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H210" t="str">
         <f>IF(G210="","",VLOOKUP(G210,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="211" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="211" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H211" t="str">
         <f>IF(G211="","",VLOOKUP(G211,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="212" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="212" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H212" t="str">
         <f>IF(G212="","",VLOOKUP(G212,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="213" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="213" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H213" t="str">
         <f>IF(G213="","",VLOOKUP(G213,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="214" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="214" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H214" t="str">
         <f>IF(G214="","",VLOOKUP(G214,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="215" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="215" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H215" t="str">
         <f>IF(G215="","",VLOOKUP(G215,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="216" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="216" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H216" t="str">
         <f>IF(G216="","",VLOOKUP(G216,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="217" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="217" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H217" t="str">
         <f>IF(G217="","",VLOOKUP(G217,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="218" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="218" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H218" t="str">
         <f>IF(G218="","",VLOOKUP(G218,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="219" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="219" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H219" t="str">
         <f>IF(G219="","",VLOOKUP(G219,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="220" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="220" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H220" t="str">
         <f>IF(G220="","",VLOOKUP(G220,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="221" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="221" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H221" t="str">
         <f>IF(G221="","",VLOOKUP(G221,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="222" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="222" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H222" t="str">
         <f>IF(G222="","",VLOOKUP(G222,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="223" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="223" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H223" t="str">
         <f>IF(G223="","",VLOOKUP(G223,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="224" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="224" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H224" t="str">
         <f>IF(G224="","",VLOOKUP(G224,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="225" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="225" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H225" t="str">
         <f>IF(G225="","",VLOOKUP(G225,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="226" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="226" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H226" t="str">
         <f>IF(G226="","",VLOOKUP(G226,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="227" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="227" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H227" t="str">
         <f>IF(G227="","",VLOOKUP(G227,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="228" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="228" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H228" t="str">
         <f>IF(G228="","",VLOOKUP(G228,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="229" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="229" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H229" t="str">
         <f>IF(G229="","",VLOOKUP(G229,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="230" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="230" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H230" t="str">
         <f>IF(G230="","",VLOOKUP(G230,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="231" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="231" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H231" t="str">
         <f>IF(G231="","",VLOOKUP(G231,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="232" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="232" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H232" t="str">
         <f>IF(G232="","",VLOOKUP(G232,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="233" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="233" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H233" t="str">
         <f>IF(G233="","",VLOOKUP(G233,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="234" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="234" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H234" t="str">
         <f>IF(G234="","",VLOOKUP(G234,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="235" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="235" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H235" t="str">
         <f>IF(G235="","",VLOOKUP(G235,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="236" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="236" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H236" t="str">
         <f>IF(G236="","",VLOOKUP(G236,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="237" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="237" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H237" t="str">
         <f>IF(G237="","",VLOOKUP(G237,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="238" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="238" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H238" t="str">
         <f>IF(G238="","",VLOOKUP(G238,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="239" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="239" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H239" t="str">
         <f>IF(G239="","",VLOOKUP(G239,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="240" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="240" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H240" t="str">
         <f>IF(G240="","",VLOOKUP(G240,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="241" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="241" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H241" t="str">
         <f>IF(G241="","",VLOOKUP(G241,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="242" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="242" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H242" t="str">
         <f>IF(G242="","",VLOOKUP(G242,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="243" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="243" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H243" t="str">
         <f>IF(G243="","",VLOOKUP(G243,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="244" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="244" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H244" t="str">
         <f>IF(G244="","",VLOOKUP(G244,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="245" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="245" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H245" t="str">
         <f>IF(G245="","",VLOOKUP(G245,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="246" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="246" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H246" t="str">
         <f>IF(G246="","",VLOOKUP(G246,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="247" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="247" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H247" t="str">
         <f>IF(G247="","",VLOOKUP(G247,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="248" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="248" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H248" t="str">
         <f>IF(G248="","",VLOOKUP(G248,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="249" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="249" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H249" t="str">
         <f>IF(G249="","",VLOOKUP(G249,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="250" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="250" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H250" t="str">
         <f>IF(G250="","",VLOOKUP(G250,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="251" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="251" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H251" t="str">
         <f>IF(G251="","",VLOOKUP(G251,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="252" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="252" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H252" t="str">
         <f>IF(G252="","",VLOOKUP(G252,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="253" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="253" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H253" t="str">
         <f>IF(G253="","",VLOOKUP(G253,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="254" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="254" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H254" t="str">
         <f>IF(G254="","",VLOOKUP(G254,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="255" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="255" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H255" t="str">
         <f>IF(G255="","",VLOOKUP(G255,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="256" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="256" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H256" t="str">
         <f>IF(G256="","",VLOOKUP(G256,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="257" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="257" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H257" t="str">
         <f>IF(G257="","",VLOOKUP(G257,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="258" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="258" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H258" t="str">
         <f>IF(G258="","",VLOOKUP(G258,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="259" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="259" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H259" t="str">
         <f>IF(G259="","",VLOOKUP(G259,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="260" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="260" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H260" t="str">
         <f>IF(G260="","",VLOOKUP(G260,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="261" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="261" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H261" t="str">
         <f>IF(G261="","",VLOOKUP(G261,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="262" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="262" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H262" t="str">
         <f>IF(G262="","",VLOOKUP(G262,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="263" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="263" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H263" t="str">
         <f>IF(G263="","",VLOOKUP(G263,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="264" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="264" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H264" t="str">
         <f>IF(G264="","",VLOOKUP(G264,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="265" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="265" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H265" t="str">
         <f>IF(G265="","",VLOOKUP(G265,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="266" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="266" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H266" t="str">
         <f>IF(G266="","",VLOOKUP(G266,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="267" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="267" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H267" t="str">
         <f>IF(G267="","",VLOOKUP(G267,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="268" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="268" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H268" t="str">
         <f>IF(G268="","",VLOOKUP(G268,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="269" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="269" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H269" t="str">
         <f>IF(G269="","",VLOOKUP(G269,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="270" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="270" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H270" t="str">
         <f>IF(G270="","",VLOOKUP(G270,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="271" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="271" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H271" t="str">
         <f>IF(G271="","",VLOOKUP(G271,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="272" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="272" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H272" t="str">
         <f>IF(G272="","",VLOOKUP(G272,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="273" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="273" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H273" t="str">
         <f>IF(G273="","",VLOOKUP(G273,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="274" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="274" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H274" t="str">
         <f>IF(G274="","",VLOOKUP(G274,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="275" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="275" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H275" t="str">
         <f>IF(G275="","",VLOOKUP(G275,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="276" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="276" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H276" t="str">
         <f>IF(G276="","",VLOOKUP(G276,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="277" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="277" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H277" t="str">
         <f>IF(G277="","",VLOOKUP(G277,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="278" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="278" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H278" t="str">
         <f>IF(G278="","",VLOOKUP(G278,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="279" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="279" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H279" t="str">
         <f>IF(G279="","",VLOOKUP(G279,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="280" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="280" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H280" t="str">
         <f>IF(G280="","",VLOOKUP(G280,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="281" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="281" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H281" t="str">
         <f>IF(G281="","",VLOOKUP(G281,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="282" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="282" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H282" t="str">
         <f>IF(G282="","",VLOOKUP(G282,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="283" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="283" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H283" t="str">
         <f>IF(G283="","",VLOOKUP(G283,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="284" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="284" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H284" t="str">
         <f>IF(G284="","",VLOOKUP(G284,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="285" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="285" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H285" t="str">
         <f>IF(G285="","",VLOOKUP(G285,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="286" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="286" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H286" t="str">
         <f>IF(G286="","",VLOOKUP(G286,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="287" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="287" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H287" t="str">
         <f>IF(G287="","",VLOOKUP(G287,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="288" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="288" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H288" t="str">
         <f>IF(G288="","",VLOOKUP(G288,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="289" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="289" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H289" t="str">
         <f>IF(G289="","",VLOOKUP(G289,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="290" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="290" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H290" t="str">
         <f>IF(G290="","",VLOOKUP(G290,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="291" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="291" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H291" t="str">
         <f>IF(G291="","",VLOOKUP(G291,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="292" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="292" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H292" t="str">
         <f>IF(G292="","",VLOOKUP(G292,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="293" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="293" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H293" t="str">
         <f>IF(G293="","",VLOOKUP(G293,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="294" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="294" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H294" t="str">
         <f>IF(G294="","",VLOOKUP(G294,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="295" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="295" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H295" t="str">
         <f>IF(G295="","",VLOOKUP(G295,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="296" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="296" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H296" t="str">
         <f>IF(G296="","",VLOOKUP(G296,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="297" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="297" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H297" t="str">
         <f>IF(G297="","",VLOOKUP(G297,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="298" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="298" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H298" t="str">
         <f>IF(G298="","",VLOOKUP(G298,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="299" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="299" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H299" t="str">
         <f>IF(G299="","",VLOOKUP(G299,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="300" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="300" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H300" t="str">
         <f>IF(G300="","",VLOOKUP(G300,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="301" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="301" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H301" t="str">
         <f>IF(G301="","",VLOOKUP(G301,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="302" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="302" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H302" t="str">
         <f>IF(G302="","",VLOOKUP(G302,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="303" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="303" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H303" t="str">
         <f>IF(G303="","",VLOOKUP(G303,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="304" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="304" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H304" t="str">
         <f>IF(G304="","",VLOOKUP(G304,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="305" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="305" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H305" t="str">
         <f>IF(G305="","",VLOOKUP(G305,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="306" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="306" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H306" t="str">
         <f>IF(G306="","",VLOOKUP(G306,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="307" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="307" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H307" t="str">
         <f>IF(G307="","",VLOOKUP(G307,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="308" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="308" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H308" t="str">
         <f>IF(G308="","",VLOOKUP(G308,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="309" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="309" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H309" t="str">
         <f>IF(G309="","",VLOOKUP(G309,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="310" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="310" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H310" t="str">
         <f>IF(G310="","",VLOOKUP(G310,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="311" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="311" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H311" t="str">
         <f>IF(G311="","",VLOOKUP(G311,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="312" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="312" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H312" t="str">
         <f>IF(G312="","",VLOOKUP(G312,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="313" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="313" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H313" t="str">
         <f>IF(G313="","",VLOOKUP(G313,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="314" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="314" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H314" t="str">
         <f>IF(G314="","",VLOOKUP(G314,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="315" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="315" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H315" t="str">
         <f>IF(G315="","",VLOOKUP(G315,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="316" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="316" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H316" t="str">
         <f>IF(G316="","",VLOOKUP(G316,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="317" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="317" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H317" t="str">
         <f>IF(G317="","",VLOOKUP(G317,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="318" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="318" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H318" t="str">
         <f>IF(G318="","",VLOOKUP(G318,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="319" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="319" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H319" t="str">
         <f>IF(G319="","",VLOOKUP(G319,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="320" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="320" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H320" t="str">
         <f>IF(G320="","",VLOOKUP(G320,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="321" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="321" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H321" t="str">
         <f>IF(G321="","",VLOOKUP(G321,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="322" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="322" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H322" t="str">
         <f>IF(G322="","",VLOOKUP(G322,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="323" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="323" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H323" t="str">
         <f>IF(G323="","",VLOOKUP(G323,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="324" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="324" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H324" t="str">
         <f>IF(G324="","",VLOOKUP(G324,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="325" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="325" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H325" t="str">
         <f>IF(G325="","",VLOOKUP(G325,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="326" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="326" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H326" t="str">
         <f>IF(G326="","",VLOOKUP(G326,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="327" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="327" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H327" t="str">
         <f>IF(G327="","",VLOOKUP(G327,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="328" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="328" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H328" t="str">
         <f>IF(G328="","",VLOOKUP(G328,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="329" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="329" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H329" t="str">
         <f>IF(G329="","",VLOOKUP(G329,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="330" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="330" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H330" t="str">
         <f>IF(G330="","",VLOOKUP(G330,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="331" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="331" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H331" t="str">
         <f>IF(G331="","",VLOOKUP(G331,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="332" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="332" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H332" t="str">
         <f>IF(G332="","",VLOOKUP(G332,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="333" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="333" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H333" t="str">
         <f>IF(G333="","",VLOOKUP(G333,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="334" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="334" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H334" t="str">
         <f>IF(G334="","",VLOOKUP(G334,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="335" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="335" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H335" t="str">
         <f>IF(G335="","",VLOOKUP(G335,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="336" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="336" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H336" t="str">
         <f>IF(G336="","",VLOOKUP(G336,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="337" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="337" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H337" t="str">
         <f>IF(G337="","",VLOOKUP(G337,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="338" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="338" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H338" t="str">
         <f>IF(G338="","",VLOOKUP(G338,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="339" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="339" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H339" t="str">
         <f>IF(G339="","",VLOOKUP(G339,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="340" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="340" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H340" t="str">
         <f>IF(G340="","",VLOOKUP(G340,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="341" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="341" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H341" t="str">
         <f>IF(G341="","",VLOOKUP(G341,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="342" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="342" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H342" t="str">
         <f>IF(G342="","",VLOOKUP(G342,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="343" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="343" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H343" t="str">
         <f>IF(G343="","",VLOOKUP(G343,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="344" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="344" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H344" t="str">
         <f>IF(G344="","",VLOOKUP(G344,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="345" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="345" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H345" t="str">
         <f>IF(G345="","",VLOOKUP(G345,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="346" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="346" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H346" t="str">
         <f>IF(G346="","",VLOOKUP(G346,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="347" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="347" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H347" t="str">
         <f>IF(G347="","",VLOOKUP(G347,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="348" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="348" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H348" t="str">
         <f>IF(G348="","",VLOOKUP(G348,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="349" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="349" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H349" t="str">
         <f>IF(G349="","",VLOOKUP(G349,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="350" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="350" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H350" t="str">
         <f>IF(G350="","",VLOOKUP(G350,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="351" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="351" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H351" t="str">
         <f>IF(G351="","",VLOOKUP(G351,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="352" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="352" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H352" t="str">
         <f>IF(G352="","",VLOOKUP(G352,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="353" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="353" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H353" t="str">
         <f>IF(G353="","",VLOOKUP(G353,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="354" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="354" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H354" t="str">
         <f>IF(G354="","",VLOOKUP(G354,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="355" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="355" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H355" t="str">
         <f>IF(G355="","",VLOOKUP(G355,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="356" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="356" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H356" t="str">
         <f>IF(G356="","",VLOOKUP(G356,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="357" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="357" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H357" t="str">
         <f>IF(G357="","",VLOOKUP(G357,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="358" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="358" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H358" t="str">
         <f>IF(G358="","",VLOOKUP(G358,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="359" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="359" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H359" t="str">
         <f>IF(G359="","",VLOOKUP(G359,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="360" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="360" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H360" t="str">
         <f>IF(G360="","",VLOOKUP(G360,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="361" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="361" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H361" t="str">
         <f>IF(G361="","",VLOOKUP(G361,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="362" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="362" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H362" t="str">
         <f>IF(G362="","",VLOOKUP(G362,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="363" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="363" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H363" t="str">
         <f>IF(G363="","",VLOOKUP(G363,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="364" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="364" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H364" t="str">
         <f>IF(G364="","",VLOOKUP(G364,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="365" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="365" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H365" t="str">
         <f>IF(G365="","",VLOOKUP(G365,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="366" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="366" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H366" t="str">
         <f>IF(G366="","",VLOOKUP(G366,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="367" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="367" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H367" t="str">
         <f>IF(G367="","",VLOOKUP(G367,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="368" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="368" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H368" t="str">
         <f>IF(G368="","",VLOOKUP(G368,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="369" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="369" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H369" t="str">
         <f>IF(G369="","",VLOOKUP(G369,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="370" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="370" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H370" t="str">
         <f>IF(G370="","",VLOOKUP(G370,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="371" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="371" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H371" t="str">
         <f>IF(G371="","",VLOOKUP(G371,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="372" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="372" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H372" t="str">
         <f>IF(G372="","",VLOOKUP(G372,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="373" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="373" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H373" t="str">
         <f>IF(G373="","",VLOOKUP(G373,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="374" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="374" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H374" t="str">
         <f>IF(G374="","",VLOOKUP(G374,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="375" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="375" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H375" t="str">
         <f>IF(G375="","",VLOOKUP(G375,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="376" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="376" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H376" t="str">
         <f>IF(G376="","",VLOOKUP(G376,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="377" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="377" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H377" t="str">
         <f>IF(G377="","",VLOOKUP(G377,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="378" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="378" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H378" t="str">
         <f>IF(G378="","",VLOOKUP(G378,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="379" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="379" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H379" t="str">
         <f>IF(G379="","",VLOOKUP(G379,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="380" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="380" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H380" t="str">
         <f>IF(G380="","",VLOOKUP(G380,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="381" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="381" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H381" t="str">
         <f>IF(G381="","",VLOOKUP(G381,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="382" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="382" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H382" t="str">
         <f>IF(G382="","",VLOOKUP(G382,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="383" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="383" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H383" t="str">
         <f>IF(G383="","",VLOOKUP(G383,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="384" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="384" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H384" t="str">
         <f>IF(G384="","",VLOOKUP(G384,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="385" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="385" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H385" t="str">
         <f>IF(G385="","",VLOOKUP(G385,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="386" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="386" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H386" t="str">
         <f>IF(G386="","",VLOOKUP(G386,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="387" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="387" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H387" t="str">
         <f>IF(G387="","",VLOOKUP(G387,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="388" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="388" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H388" t="str">
         <f>IF(G388="","",VLOOKUP(G388,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="389" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="389" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H389" t="str">
         <f>IF(G389="","",VLOOKUP(G389,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="390" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="390" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H390" t="str">
         <f>IF(G390="","",VLOOKUP(G390,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="391" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="391" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H391" t="str">
         <f>IF(G391="","",VLOOKUP(G391,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="392" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="392" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H392" t="str">
         <f>IF(G392="","",VLOOKUP(G392,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="393" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="393" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H393" t="str">
         <f>IF(G393="","",VLOOKUP(G393,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="394" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="394" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H394" t="str">
         <f>IF(G394="","",VLOOKUP(G394,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="395" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="395" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H395" t="str">
         <f>IF(G395="","",VLOOKUP(G395,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="396" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="396" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H396" t="str">
         <f>IF(G396="","",VLOOKUP(G396,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="397" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="397" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H397" t="str">
         <f>IF(G397="","",VLOOKUP(G397,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="398" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="398" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H398" t="str">
         <f>IF(G398="","",VLOOKUP(G398,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="399" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="399" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H399" t="str">
         <f>IF(G399="","",VLOOKUP(G399,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="400" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="400" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H400" t="str">
         <f>IF(G400="","",VLOOKUP(G400,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="401" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="401" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H401" t="str">
         <f>IF(G401="","",VLOOKUP(G401,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="402" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="402" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H402" t="str">
         <f>IF(G402="","",VLOOKUP(G402,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="403" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="403" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H403" t="str">
         <f>IF(G403="","",VLOOKUP(G403,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="404" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="404" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H404" t="str">
         <f>IF(G404="","",VLOOKUP(G404,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="405" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="405" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H405" t="str">
         <f>IF(G405="","",VLOOKUP(G405,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="406" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="406" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H406" t="str">
         <f>IF(G406="","",VLOOKUP(G406,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="407" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="407" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H407" t="str">
         <f>IF(G407="","",VLOOKUP(G407,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="408" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="408" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H408" t="str">
         <f>IF(G408="","",VLOOKUP(G408,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="409" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="409" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H409" t="str">
         <f>IF(G409="","",VLOOKUP(G409,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="410" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="410" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H410" t="str">
         <f>IF(G410="","",VLOOKUP(G410,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="411" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="411" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H411" t="str">
         <f>IF(G411="","",VLOOKUP(G411,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="412" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="412" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H412" t="str">
         <f>IF(G412="","",VLOOKUP(G412,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="413" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="413" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H413" t="str">
         <f>IF(G413="","",VLOOKUP(G413,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="414" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="414" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H414" t="str">
         <f>IF(G414="","",VLOOKUP(G414,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="415" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="415" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H415" t="str">
         <f>IF(G415="","",VLOOKUP(G415,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="416" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="416" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H416" t="str">
         <f>IF(G416="","",VLOOKUP(G416,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="417" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="417" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H417" t="str">
         <f>IF(G417="","",VLOOKUP(G417,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="418" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="418" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H418" t="str">
         <f>IF(G418="","",VLOOKUP(G418,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="419" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="419" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H419" t="str">
         <f>IF(G419="","",VLOOKUP(G419,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="420" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="420" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H420" t="str">
         <f>IF(G420="","",VLOOKUP(G420,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="421" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="421" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H421" t="str">
         <f>IF(G421="","",VLOOKUP(G421,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="422" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="422" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H422" t="str">
         <f>IF(G422="","",VLOOKUP(G422,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="423" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="423" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H423" t="str">
         <f>IF(G423="","",VLOOKUP(G423,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="424" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="424" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H424" t="str">
         <f>IF(G424="","",VLOOKUP(G424,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="425" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="425" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H425" t="str">
         <f>IF(G425="","",VLOOKUP(G425,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="426" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="426" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H426" t="str">
         <f>IF(G426="","",VLOOKUP(G426,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="427" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="427" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H427" t="str">
         <f>IF(G427="","",VLOOKUP(G427,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="428" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="428" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H428" t="str">
         <f>IF(G428="","",VLOOKUP(G428,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="429" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="429" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H429" t="str">
         <f>IF(G429="","",VLOOKUP(G429,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="430" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="430" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H430" t="str">
         <f>IF(G430="","",VLOOKUP(G430,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="431" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="431" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H431" t="str">
         <f>IF(G431="","",VLOOKUP(G431,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="432" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="432" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H432" t="str">
         <f>IF(G432="","",VLOOKUP(G432,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="433" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="433" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H433" t="str">
         <f>IF(G433="","",VLOOKUP(G433,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="434" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="434" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H434" t="str">
         <f>IF(G434="","",VLOOKUP(G434,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="435" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="435" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H435" t="str">
         <f>IF(G435="","",VLOOKUP(G435,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="436" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="436" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H436" t="str">
         <f>IF(G436="","",VLOOKUP(G436,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="437" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="437" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H437" t="str">
         <f>IF(G437="","",VLOOKUP(G437,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="438" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="438" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H438" t="str">
         <f>IF(G438="","",VLOOKUP(G438,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="439" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="439" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H439" t="str">
         <f>IF(G439="","",VLOOKUP(G439,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="440" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="440" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H440" t="str">
         <f>IF(G440="","",VLOOKUP(G440,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="441" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="441" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H441" t="str">
         <f>IF(G441="","",VLOOKUP(G441,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="442" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="442" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H442" t="str">
         <f>IF(G442="","",VLOOKUP(G442,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="443" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="443" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H443" t="str">
         <f>IF(G443="","",VLOOKUP(G443,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="444" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="444" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H444" t="str">
         <f>IF(G444="","",VLOOKUP(G444,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="445" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="445" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H445" t="str">
         <f>IF(G445="","",VLOOKUP(G445,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="446" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="446" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H446" t="str">
         <f>IF(G446="","",VLOOKUP(G446,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="447" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="447" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H447" t="str">
         <f>IF(G447="","",VLOOKUP(G447,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="448" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="448" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H448" t="str">
         <f>IF(G448="","",VLOOKUP(G448,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="449" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="449" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H449" t="str">
         <f>IF(G449="","",VLOOKUP(G449,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="450" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="450" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H450" t="str">
         <f>IF(G450="","",VLOOKUP(G450,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="451" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="451" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H451" t="str">
         <f>IF(G451="","",VLOOKUP(G451,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="452" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="452" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H452" t="str">
         <f>IF(G452="","",VLOOKUP(G452,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="453" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="453" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H453" t="str">
         <f>IF(G453="","",VLOOKUP(G453,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="454" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="454" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H454" t="str">
         <f>IF(G454="","",VLOOKUP(G454,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="455" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="455" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H455" t="str">
         <f>IF(G455="","",VLOOKUP(G455,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="456" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="456" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H456" t="str">
         <f>IF(G456="","",VLOOKUP(G456,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="457" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="457" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H457" t="str">
         <f>IF(G457="","",VLOOKUP(G457,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="458" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="458" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H458" t="str">
         <f>IF(G458="","",VLOOKUP(G458,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="459" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="459" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H459" t="str">
         <f>IF(G459="","",VLOOKUP(G459,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="460" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="460" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H460" t="str">
         <f>IF(G460="","",VLOOKUP(G460,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="461" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="461" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H461" t="str">
         <f>IF(G461="","",VLOOKUP(G461,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="462" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="462" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H462" t="str">
         <f>IF(G462="","",VLOOKUP(G462,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="463" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="463" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H463" t="str">
         <f>IF(G463="","",VLOOKUP(G463,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="464" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="464" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H464" t="str">
         <f>IF(G464="","",VLOOKUP(G464,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="465" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="465" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H465" t="str">
         <f>IF(G465="","",VLOOKUP(G465,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="466" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="466" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H466" t="str">
         <f>IF(G466="","",VLOOKUP(G466,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="467" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="467" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H467" t="str">
         <f>IF(G467="","",VLOOKUP(G467,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="468" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="468" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H468" t="str">
         <f>IF(G468="","",VLOOKUP(G468,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="469" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="469" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H469" t="str">
         <f>IF(G469="","",VLOOKUP(G469,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="470" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="470" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H470" t="str">
         <f>IF(G470="","",VLOOKUP(G470,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="471" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="471" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H471" t="str">
         <f>IF(G471="","",VLOOKUP(G471,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="472" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="472" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H472" t="str">
         <f>IF(G472="","",VLOOKUP(G472,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="473" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="473" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H473" t="str">
         <f>IF(G473="","",VLOOKUP(G473,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="474" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="474" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H474" t="str">
         <f>IF(G474="","",VLOOKUP(G474,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="475" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="475" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H475" t="str">
         <f>IF(G475="","",VLOOKUP(G475,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="476" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="476" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H476" t="str">
         <f>IF(G476="","",VLOOKUP(G476,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="477" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="477" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H477" t="str">
         <f>IF(G477="","",VLOOKUP(G477,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="478" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="478" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H478" t="str">
         <f>IF(G478="","",VLOOKUP(G478,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="479" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="479" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H479" t="str">
         <f>IF(G479="","",VLOOKUP(G479,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="480" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="480" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H480" t="str">
         <f>IF(G480="","",VLOOKUP(G480,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="481" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="481" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H481" t="str">
         <f>IF(G481="","",VLOOKUP(G481,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="482" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="482" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H482" t="str">
         <f>IF(G482="","",VLOOKUP(G482,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="483" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="483" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H483" t="str">
         <f>IF(G483="","",VLOOKUP(G483,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="484" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="484" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H484" t="str">
         <f>IF(G484="","",VLOOKUP(G484,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="485" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="485" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H485" t="str">
         <f>IF(G485="","",VLOOKUP(G485,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="486" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="486" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H486" t="str">
         <f>IF(G486="","",VLOOKUP(G486,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="487" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="487" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H487" t="str">
         <f>IF(G487="","",VLOOKUP(G487,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="488" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="488" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H488" t="str">
         <f>IF(G488="","",VLOOKUP(G488,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="489" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="489" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H489" t="str">
         <f>IF(G489="","",VLOOKUP(G489,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="490" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="490" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H490" t="str">
         <f>IF(G490="","",VLOOKUP(G490,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="491" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="491" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H491" t="str">
         <f>IF(G491="","",VLOOKUP(G491,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="492" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="492" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H492" t="str">
         <f>IF(G492="","",VLOOKUP(G492,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="493" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="493" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H493" t="str">
         <f>IF(G493="","",VLOOKUP(G493,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="494" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="494" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H494" t="str">
         <f>IF(G494="","",VLOOKUP(G494,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="495" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="495" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H495" t="str">
         <f>IF(G495="","",VLOOKUP(G495,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="496" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="496" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H496" t="str">
         <f>IF(G496="","",VLOOKUP(G496,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="497" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="497" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H497" t="str">
         <f>IF(G497="","",VLOOKUP(G497,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="498" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="498" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H498" t="str">
         <f>IF(G498="","",VLOOKUP(G498,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="499" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="499" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H499" t="str">
         <f>IF(G499="","",VLOOKUP(G499,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="500" spans="8:8" x14ac:dyDescent="0.5">
+    <row r="500" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H500" t="str">
         <f>IF(G500="","",VLOOKUP(G500,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
@@ -5566,7 +5560,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1">
           <x14:formula1>
             <xm:f>REFERENCIA!$A$1:$A$15</xm:f>
           </x14:formula1>
@@ -5579,11 +5573,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.9375" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -5591,7 +5585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -5607,7 +5601,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -5615,7 +5609,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -5631,7 +5625,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -5639,7 +5633,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -5655,7 +5649,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -5663,7 +5657,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -5671,7 +5665,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -5687,7 +5681,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>28</v>
       </c>

--- a/cuadros/ABRIL/Abril_Acasias_villas.xlsx
+++ b/cuadros/ABRIL/Abril_Acasias_villas.xlsx
@@ -1,16 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\FISCALIZACION\cuadros\ABRIL\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8499A463-5FE3-4E1F-9C01-7DB739E75024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23256" windowHeight="13176"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="REFERENCIA" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -616,7 +634,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -767,7 +785,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -835,7 +853,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1137,9 +1158,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K500"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.84375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -1153,7 +1174,7 @@
     <col min="11" max="11" width="12" style="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1188,7 +1209,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
@@ -1219,7 +1240,7 @@
       </c>
       <c r="J2" s="9"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>177</v>
       </c>
@@ -1255,7 +1276,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>177</v>
       </c>
@@ -1286,7 +1307,7 @@
       </c>
       <c r="J4" s="9"/>
     </row>
-    <row r="5" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>31</v>
       </c>
@@ -1314,7 +1335,7 @@
       </c>
       <c r="J5" s="9"/>
     </row>
-    <row r="6" spans="1:11" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="77.150000000000006" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>31</v>
       </c>
@@ -1343,11 +1364,11 @@
       <c r="I6" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="J6" s="16" t="s">
+      <c r="J6" s="25" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>177</v>
       </c>
@@ -1378,7 +1399,7 @@
       </c>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>177</v>
       </c>
@@ -1407,11 +1428,11 @@
       <c r="I8" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="25">
         <v>426</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
         <v>177</v>
       </c>
@@ -1442,7 +1463,7 @@
       </c>
       <c r="J9" s="9"/>
     </row>
-    <row r="10" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
         <v>177</v>
       </c>
@@ -1478,7 +1499,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
         <v>177</v>
       </c>
@@ -1514,7 +1535,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
         <v>177</v>
       </c>
@@ -1545,7 +1566,7 @@
       </c>
       <c r="J12" s="9"/>
     </row>
-    <row r="13" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A13" s="2" t="s">
         <v>31</v>
       </c>
@@ -1576,7 +1597,7 @@
       </c>
       <c r="J13" s="9"/>
     </row>
-    <row r="14" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
         <v>31</v>
       </c>
@@ -1607,7 +1628,7 @@
       </c>
       <c r="J14" s="9"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
         <v>177</v>
       </c>
@@ -1638,7 +1659,7 @@
       </c>
       <c r="J15" s="9"/>
     </row>
-    <row r="16" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
         <v>31</v>
       </c>
@@ -1667,11 +1688,11 @@
       <c r="I16" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="J16" s="16" t="s">
+      <c r="J16" s="25" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="s">
         <v>31</v>
       </c>
@@ -1702,7 +1723,7 @@
       </c>
       <c r="J17" s="9"/>
     </row>
-    <row r="18" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="38.6" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
         <v>177</v>
       </c>
@@ -1733,7 +1754,7 @@
       </c>
       <c r="J18" s="9"/>
     </row>
-    <row r="19" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A19" s="2" t="s">
         <v>31</v>
       </c>
@@ -1764,7 +1785,7 @@
       </c>
       <c r="J19" s="9"/>
     </row>
-    <row r="20" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A20" s="2" t="s">
         <v>31</v>
       </c>
@@ -1795,7 +1816,7 @@
       </c>
       <c r="J20" s="9"/>
     </row>
-    <row r="21" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A21" s="2" t="s">
         <v>31</v>
       </c>
@@ -1826,7 +1847,7 @@
       </c>
       <c r="J21" s="9"/>
     </row>
-    <row r="22" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A22" s="2" t="s">
         <v>31</v>
       </c>
@@ -1862,7 +1883,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A23" s="2" t="s">
         <v>177</v>
       </c>
@@ -1898,7 +1919,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A24" s="2" t="s">
         <v>177</v>
       </c>
@@ -1929,7 +1950,7 @@
       </c>
       <c r="J24" s="9"/>
     </row>
-    <row r="25" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A25" s="2" t="s">
         <v>177</v>
       </c>
@@ -1960,7 +1981,7 @@
       </c>
       <c r="J25" s="9"/>
     </row>
-    <row r="26" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A26" s="2" t="s">
         <v>31</v>
       </c>
@@ -1991,7 +2012,7 @@
       </c>
       <c r="J26" s="9"/>
     </row>
-    <row r="27" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A27" s="2" t="s">
         <v>177</v>
       </c>
@@ -2022,7 +2043,7 @@
       </c>
       <c r="J27" s="9"/>
     </row>
-    <row r="28" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A28" s="2" t="s">
         <v>31</v>
       </c>
@@ -2053,7 +2074,7 @@
       </c>
       <c r="J28" s="9"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A29" s="2" t="s">
         <v>177</v>
       </c>
@@ -2084,7 +2105,7 @@
       </c>
       <c r="J29" s="9"/>
     </row>
-    <row r="30" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A30" s="2" t="s">
         <v>177</v>
       </c>
@@ -2115,7 +2136,7 @@
       </c>
       <c r="J30" s="9"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A31" s="2" t="s">
         <v>177</v>
       </c>
@@ -2146,7 +2167,7 @@
       </c>
       <c r="J31" s="9"/>
     </row>
-    <row r="32" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A32" s="2" t="s">
         <v>177</v>
       </c>
@@ -2177,7 +2198,7 @@
       </c>
       <c r="J32" s="9"/>
     </row>
-    <row r="33" spans="1:11" ht="69" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" ht="64.3" x14ac:dyDescent="0.4">
       <c r="A33" s="2" t="s">
         <v>31</v>
       </c>
@@ -2210,7 +2231,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A34" s="2" t="s">
         <v>31</v>
       </c>
@@ -2246,7 +2267,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A35" s="2" t="s">
         <v>177</v>
       </c>
@@ -2282,7 +2303,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
         <v>177</v>
       </c>
@@ -2313,7 +2334,7 @@
       </c>
       <c r="J36" s="9"/>
     </row>
-    <row r="37" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
         <v>177</v>
       </c>
@@ -2349,7 +2370,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
         <v>177</v>
       </c>
@@ -2382,7 +2403,7 @@
         <v>124.3</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
         <v>177</v>
       </c>
@@ -2418,7 +2439,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
         <v>177</v>
       </c>
@@ -2449,7 +2470,7 @@
       </c>
       <c r="J40" s="17"/>
     </row>
-    <row r="41" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A41" s="2" t="s">
         <v>31</v>
       </c>
@@ -2479,7 +2500,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A42" s="2" t="s">
         <v>31</v>
       </c>
@@ -2509,7 +2530,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A43" s="2" t="s">
         <v>177</v>
       </c>
@@ -2539,7 +2560,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" ht="23.15" x14ac:dyDescent="0.4">
       <c r="A44" s="2" t="s">
         <v>31</v>
       </c>
@@ -2569,7 +2590,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A45" s="2" t="s">
         <v>177</v>
       </c>
@@ -2599,7 +2620,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" ht="24.9" x14ac:dyDescent="0.4">
       <c r="A46" s="2" t="s">
         <v>31</v>
       </c>
@@ -2629,7 +2650,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A47" s="2" t="s">
         <v>31</v>
       </c>
@@ -2659,7 +2680,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A48" s="2" t="s">
         <v>177</v>
       </c>
@@ -2689,7 +2710,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A49" s="2" t="s">
         <v>177</v>
       </c>
@@ -2719,7 +2740,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A50" s="2" t="s">
         <v>31</v>
       </c>
@@ -2749,7 +2770,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A51" s="2" t="s">
         <v>31</v>
       </c>
@@ -2779,7 +2800,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" ht="24" x14ac:dyDescent="0.4">
       <c r="A52" s="2" t="s">
         <v>31</v>
       </c>
@@ -2809,7 +2830,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="69" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" ht="64.75" x14ac:dyDescent="0.4">
       <c r="A53" s="2" t="s">
         <v>31</v>
       </c>
@@ -2838,11 +2859,11 @@
       <c r="I53" s="24" t="s">
         <v>194</v>
       </c>
-      <c r="J53" s="25">
+      <c r="J53" s="26">
         <v>380.82</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A54" s="2" t="s">
         <v>177</v>
       </c>
@@ -2878,2677 +2899,2677 @@
         <v>191</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H55" t="str">
         <f>IF(G55="","",VLOOKUP(G55,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H56" t="str">
         <f>IF(G56="","",VLOOKUP(G56,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H57" t="str">
         <f>IF(G57="","",VLOOKUP(G57,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H58" t="str">
         <f>IF(G58="","",VLOOKUP(G58,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H59" t="str">
         <f>IF(G59="","",VLOOKUP(G59,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H60" t="str">
         <f>IF(G60="","",VLOOKUP(G60,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H61" t="str">
         <f>IF(G61="","",VLOOKUP(G61,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H62" t="str">
         <f>IF(G62="","",VLOOKUP(G62,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H63" t="str">
         <f>IF(G63="","",VLOOKUP(G63,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.4">
       <c r="H64" t="str">
         <f>IF(G64="","",VLOOKUP(G64,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="65" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H65" t="str">
         <f>IF(G65="","",VLOOKUP(G65,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="66" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H66" t="str">
         <f>IF(G66="","",VLOOKUP(G66,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="67" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H67" t="str">
         <f>IF(G67="","",VLOOKUP(G67,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="68" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H68" t="str">
         <f>IF(G68="","",VLOOKUP(G68,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="69" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H69" t="str">
         <f>IF(G69="","",VLOOKUP(G69,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="70" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H70" t="str">
         <f>IF(G70="","",VLOOKUP(G70,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="71" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H71" t="str">
         <f>IF(G71="","",VLOOKUP(G71,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="72" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H72" t="str">
         <f>IF(G72="","",VLOOKUP(G72,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="73" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H73" t="str">
         <f>IF(G73="","",VLOOKUP(G73,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="74" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H74" t="str">
         <f>IF(G74="","",VLOOKUP(G74,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="75" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H75" t="str">
         <f>IF(G75="","",VLOOKUP(G75,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="76" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H76" t="str">
         <f>IF(G76="","",VLOOKUP(G76,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="77" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H77" t="str">
         <f>IF(G77="","",VLOOKUP(G77,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="78" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H78" t="str">
         <f>IF(G78="","",VLOOKUP(G78,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="79" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H79" t="str">
         <f>IF(G79="","",VLOOKUP(G79,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="80" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H80" t="str">
         <f>IF(G80="","",VLOOKUP(G80,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="81" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H81" t="str">
         <f>IF(G81="","",VLOOKUP(G81,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="82" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H82" t="str">
         <f>IF(G82="","",VLOOKUP(G82,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="83" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H83" t="str">
         <f>IF(G83="","",VLOOKUP(G83,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="84" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H84" t="str">
         <f>IF(G84="","",VLOOKUP(G84,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="85" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H85" t="str">
         <f>IF(G85="","",VLOOKUP(G85,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="86" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H86" t="str">
         <f>IF(G86="","",VLOOKUP(G86,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="87" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H87" t="str">
         <f>IF(G87="","",VLOOKUP(G87,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="88" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H88" t="str">
         <f>IF(G88="","",VLOOKUP(G88,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="89" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H89" t="str">
         <f>IF(G89="","",VLOOKUP(G89,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="90" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H90" t="str">
         <f>IF(G90="","",VLOOKUP(G90,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="91" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H91" t="str">
         <f>IF(G91="","",VLOOKUP(G91,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="92" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H92" t="str">
         <f>IF(G92="","",VLOOKUP(G92,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="93" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H93" t="str">
         <f>IF(G93="","",VLOOKUP(G93,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="94" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H94" t="str">
         <f>IF(G94="","",VLOOKUP(G94,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="95" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H95" t="str">
         <f>IF(G95="","",VLOOKUP(G95,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="96" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H96" t="str">
         <f>IF(G96="","",VLOOKUP(G96,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="97" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H97" t="str">
         <f>IF(G97="","",VLOOKUP(G97,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="98" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H98" t="str">
         <f>IF(G98="","",VLOOKUP(G98,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="99" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H99" t="str">
         <f>IF(G99="","",VLOOKUP(G99,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="100" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H100" t="str">
         <f>IF(G100="","",VLOOKUP(G100,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="101" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H101" t="str">
         <f>IF(G101="","",VLOOKUP(G101,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="102" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H102" t="str">
         <f>IF(G102="","",VLOOKUP(G102,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="103" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H103" t="str">
         <f>IF(G103="","",VLOOKUP(G103,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="104" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H104" t="str">
         <f>IF(G104="","",VLOOKUP(G104,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="105" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H105" t="str">
         <f>IF(G105="","",VLOOKUP(G105,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="106" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H106" t="str">
         <f>IF(G106="","",VLOOKUP(G106,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="107" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H107" t="str">
         <f>IF(G107="","",VLOOKUP(G107,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="108" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H108" t="str">
         <f>IF(G108="","",VLOOKUP(G108,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="109" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H109" t="str">
         <f>IF(G109="","",VLOOKUP(G109,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="110" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H110" t="str">
         <f>IF(G110="","",VLOOKUP(G110,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="111" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H111" t="str">
         <f>IF(G111="","",VLOOKUP(G111,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="112" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H112" t="str">
         <f>IF(G112="","",VLOOKUP(G112,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="113" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H113" t="str">
         <f>IF(G113="","",VLOOKUP(G113,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="114" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H114" t="str">
         <f>IF(G114="","",VLOOKUP(G114,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="115" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H115" t="str">
         <f>IF(G115="","",VLOOKUP(G115,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="116" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H116" t="str">
         <f>IF(G116="","",VLOOKUP(G116,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="117" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H117" t="str">
         <f>IF(G117="","",VLOOKUP(G117,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="118" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H118" t="str">
         <f>IF(G118="","",VLOOKUP(G118,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="119" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H119" t="str">
         <f>IF(G119="","",VLOOKUP(G119,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="120" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H120" t="str">
         <f>IF(G120="","",VLOOKUP(G120,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="121" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H121" t="str">
         <f>IF(G121="","",VLOOKUP(G121,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="122" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H122" t="str">
         <f>IF(G122="","",VLOOKUP(G122,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="123" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H123" t="str">
         <f>IF(G123="","",VLOOKUP(G123,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="124" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H124" t="str">
         <f>IF(G124="","",VLOOKUP(G124,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="125" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H125" t="str">
         <f>IF(G125="","",VLOOKUP(G125,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H126" t="str">
         <f>IF(G126="","",VLOOKUP(G126,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H127" t="str">
         <f>IF(G127="","",VLOOKUP(G127,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="128" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H128" t="str">
         <f>IF(G128="","",VLOOKUP(G128,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="129" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H129" t="str">
         <f>IF(G129="","",VLOOKUP(G129,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="130" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H130" t="str">
         <f>IF(G130="","",VLOOKUP(G130,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="131" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H131" t="str">
         <f>IF(G131="","",VLOOKUP(G131,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="132" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H132" t="str">
         <f>IF(G132="","",VLOOKUP(G132,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="133" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H133" t="str">
         <f>IF(G133="","",VLOOKUP(G133,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="134" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H134" t="str">
         <f>IF(G134="","",VLOOKUP(G134,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="135" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H135" t="str">
         <f>IF(G135="","",VLOOKUP(G135,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="136" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H136" t="str">
         <f>IF(G136="","",VLOOKUP(G136,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="137" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H137" t="str">
         <f>IF(G137="","",VLOOKUP(G137,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="138" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H138" t="str">
         <f>IF(G138="","",VLOOKUP(G138,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="139" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="139" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H139" t="str">
         <f>IF(G139="","",VLOOKUP(G139,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="140" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="140" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H140" t="str">
         <f>IF(G140="","",VLOOKUP(G140,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="141" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H141" t="str">
         <f>IF(G141="","",VLOOKUP(G141,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="142" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H142" t="str">
         <f>IF(G142="","",VLOOKUP(G142,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="143" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="143" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H143" t="str">
         <f>IF(G143="","",VLOOKUP(G143,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="144" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="144" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H144" t="str">
         <f>IF(G144="","",VLOOKUP(G144,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="145" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H145" t="str">
         <f>IF(G145="","",VLOOKUP(G145,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="146" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="146" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H146" t="str">
         <f>IF(G146="","",VLOOKUP(G146,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="147" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="147" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H147" t="str">
         <f>IF(G147="","",VLOOKUP(G147,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="148" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="148" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H148" t="str">
         <f>IF(G148="","",VLOOKUP(G148,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="149" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H149" t="str">
         <f>IF(G149="","",VLOOKUP(G149,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="150" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H150" t="str">
         <f>IF(G150="","",VLOOKUP(G150,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="151" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H151" t="str">
         <f>IF(G151="","",VLOOKUP(G151,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="152" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H152" t="str">
         <f>IF(G152="","",VLOOKUP(G152,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="153" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="153" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H153" t="str">
         <f>IF(G153="","",VLOOKUP(G153,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="154" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="154" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H154" t="str">
         <f>IF(G154="","",VLOOKUP(G154,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="155" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="155" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H155" t="str">
         <f>IF(G155="","",VLOOKUP(G155,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="156" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="156" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H156" t="str">
         <f>IF(G156="","",VLOOKUP(G156,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="157" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="157" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H157" t="str">
         <f>IF(G157="","",VLOOKUP(G157,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="158" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="158" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H158" t="str">
         <f>IF(G158="","",VLOOKUP(G158,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="159" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="159" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H159" t="str">
         <f>IF(G159="","",VLOOKUP(G159,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="160" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="160" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H160" t="str">
         <f>IF(G160="","",VLOOKUP(G160,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="161" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="161" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H161" t="str">
         <f>IF(G161="","",VLOOKUP(G161,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="162" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="162" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H162" t="str">
         <f>IF(G162="","",VLOOKUP(G162,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="163" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="163" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H163" t="str">
         <f>IF(G163="","",VLOOKUP(G163,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="164" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="164" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H164" t="str">
         <f>IF(G164="","",VLOOKUP(G164,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="165" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="165" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H165" t="str">
         <f>IF(G165="","",VLOOKUP(G165,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="166" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="166" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H166" t="str">
         <f>IF(G166="","",VLOOKUP(G166,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="167" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="167" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H167" t="str">
         <f>IF(G167="","",VLOOKUP(G167,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="168" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="168" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H168" t="str">
         <f>IF(G168="","",VLOOKUP(G168,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="169" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="169" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H169" t="str">
         <f>IF(G169="","",VLOOKUP(G169,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="170" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="170" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H170" t="str">
         <f>IF(G170="","",VLOOKUP(G170,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="171" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="171" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H171" t="str">
         <f>IF(G171="","",VLOOKUP(G171,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="172" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="172" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H172" t="str">
         <f>IF(G172="","",VLOOKUP(G172,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="173" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="173" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H173" t="str">
         <f>IF(G173="","",VLOOKUP(G173,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="174" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="174" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H174" t="str">
         <f>IF(G174="","",VLOOKUP(G174,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="175" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="175" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H175" t="str">
         <f>IF(G175="","",VLOOKUP(G175,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="176" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="176" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H176" t="str">
         <f>IF(G176="","",VLOOKUP(G176,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="177" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="177" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H177" t="str">
         <f>IF(G177="","",VLOOKUP(G177,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="178" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="178" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H178" t="str">
         <f>IF(G178="","",VLOOKUP(G178,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="179" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="179" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H179" t="str">
         <f>IF(G179="","",VLOOKUP(G179,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="180" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="180" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H180" t="str">
         <f>IF(G180="","",VLOOKUP(G180,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="181" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="181" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H181" t="str">
         <f>IF(G181="","",VLOOKUP(G181,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="182" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="182" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H182" t="str">
         <f>IF(G182="","",VLOOKUP(G182,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="183" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="183" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H183" t="str">
         <f>IF(G183="","",VLOOKUP(G183,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="184" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="184" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H184" t="str">
         <f>IF(G184="","",VLOOKUP(G184,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="185" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="185" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H185" t="str">
         <f>IF(G185="","",VLOOKUP(G185,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="186" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="186" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H186" t="str">
         <f>IF(G186="","",VLOOKUP(G186,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="187" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="187" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H187" t="str">
         <f>IF(G187="","",VLOOKUP(G187,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="188" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="188" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H188" t="str">
         <f>IF(G188="","",VLOOKUP(G188,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="189" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="189" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H189" t="str">
         <f>IF(G189="","",VLOOKUP(G189,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="190" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="190" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H190" t="str">
         <f>IF(G190="","",VLOOKUP(G190,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="191" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="191" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H191" t="str">
         <f>IF(G191="","",VLOOKUP(G191,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="192" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="192" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H192" t="str">
         <f>IF(G192="","",VLOOKUP(G192,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="193" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H193" t="str">
         <f>IF(G193="","",VLOOKUP(G193,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="194" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H194" t="str">
         <f>IF(G194="","",VLOOKUP(G194,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="195" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H195" t="str">
         <f>IF(G195="","",VLOOKUP(G195,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="196" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H196" t="str">
         <f>IF(G196="","",VLOOKUP(G196,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="197" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="197" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H197" t="str">
         <f>IF(G197="","",VLOOKUP(G197,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="198" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="198" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H198" t="str">
         <f>IF(G198="","",VLOOKUP(G198,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="199" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="199" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H199" t="str">
         <f>IF(G199="","",VLOOKUP(G199,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="200" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="200" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H200" t="str">
         <f>IF(G200="","",VLOOKUP(G200,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="201" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H201" t="str">
         <f>IF(G201="","",VLOOKUP(G201,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="202" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H202" t="str">
         <f>IF(G202="","",VLOOKUP(G202,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="203" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="203" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H203" t="str">
         <f>IF(G203="","",VLOOKUP(G203,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="204" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H204" t="str">
         <f>IF(G204="","",VLOOKUP(G204,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="205" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="205" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H205" t="str">
         <f>IF(G205="","",VLOOKUP(G205,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="206" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H206" t="str">
         <f>IF(G206="","",VLOOKUP(G206,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="207" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="207" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H207" t="str">
         <f>IF(G207="","",VLOOKUP(G207,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="208" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="208" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H208" t="str">
         <f>IF(G208="","",VLOOKUP(G208,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="209" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H209" t="str">
         <f>IF(G209="","",VLOOKUP(G209,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="210" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H210" t="str">
         <f>IF(G210="","",VLOOKUP(G210,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="211" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="211" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H211" t="str">
         <f>IF(G211="","",VLOOKUP(G211,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="212" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="212" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H212" t="str">
         <f>IF(G212="","",VLOOKUP(G212,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="213" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="213" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H213" t="str">
         <f>IF(G213="","",VLOOKUP(G213,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="214" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H214" t="str">
         <f>IF(G214="","",VLOOKUP(G214,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="215" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="215" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H215" t="str">
         <f>IF(G215="","",VLOOKUP(G215,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="216" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="216" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H216" t="str">
         <f>IF(G216="","",VLOOKUP(G216,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="217" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="217" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H217" t="str">
         <f>IF(G217="","",VLOOKUP(G217,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="218" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H218" t="str">
         <f>IF(G218="","",VLOOKUP(G218,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="219" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H219" t="str">
         <f>IF(G219="","",VLOOKUP(G219,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="220" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H220" t="str">
         <f>IF(G220="","",VLOOKUP(G220,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="221" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H221" t="str">
         <f>IF(G221="","",VLOOKUP(G221,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="222" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H222" t="str">
         <f>IF(G222="","",VLOOKUP(G222,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="223" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="223" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H223" t="str">
         <f>IF(G223="","",VLOOKUP(G223,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="224" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="224" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H224" t="str">
         <f>IF(G224="","",VLOOKUP(G224,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="225" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="225" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H225" t="str">
         <f>IF(G225="","",VLOOKUP(G225,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="226" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="226" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H226" t="str">
         <f>IF(G226="","",VLOOKUP(G226,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="227" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="227" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H227" t="str">
         <f>IF(G227="","",VLOOKUP(G227,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="228" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="228" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H228" t="str">
         <f>IF(G228="","",VLOOKUP(G228,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="229" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="229" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H229" t="str">
         <f>IF(G229="","",VLOOKUP(G229,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="230" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="230" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H230" t="str">
         <f>IF(G230="","",VLOOKUP(G230,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="231" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="231" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H231" t="str">
         <f>IF(G231="","",VLOOKUP(G231,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="232" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="232" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H232" t="str">
         <f>IF(G232="","",VLOOKUP(G232,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="233" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="233" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H233" t="str">
         <f>IF(G233="","",VLOOKUP(G233,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="234" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="234" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H234" t="str">
         <f>IF(G234="","",VLOOKUP(G234,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="235" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="235" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H235" t="str">
         <f>IF(G235="","",VLOOKUP(G235,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="236" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="236" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H236" t="str">
         <f>IF(G236="","",VLOOKUP(G236,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="237" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="237" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H237" t="str">
         <f>IF(G237="","",VLOOKUP(G237,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="238" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="238" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H238" t="str">
         <f>IF(G238="","",VLOOKUP(G238,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="239" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="239" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H239" t="str">
         <f>IF(G239="","",VLOOKUP(G239,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="240" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="240" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H240" t="str">
         <f>IF(G240="","",VLOOKUP(G240,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="241" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="241" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H241" t="str">
         <f>IF(G241="","",VLOOKUP(G241,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="242" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="242" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H242" t="str">
         <f>IF(G242="","",VLOOKUP(G242,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="243" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="243" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H243" t="str">
         <f>IF(G243="","",VLOOKUP(G243,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="244" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="244" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H244" t="str">
         <f>IF(G244="","",VLOOKUP(G244,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="245" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H245" t="str">
         <f>IF(G245="","",VLOOKUP(G245,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="246" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H246" t="str">
         <f>IF(G246="","",VLOOKUP(G246,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="247" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H247" t="str">
         <f>IF(G247="","",VLOOKUP(G247,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="248" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="248" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H248" t="str">
         <f>IF(G248="","",VLOOKUP(G248,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="249" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H249" t="str">
         <f>IF(G249="","",VLOOKUP(G249,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="250" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="250" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H250" t="str">
         <f>IF(G250="","",VLOOKUP(G250,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="251" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="251" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H251" t="str">
         <f>IF(G251="","",VLOOKUP(G251,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="252" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="252" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H252" t="str">
         <f>IF(G252="","",VLOOKUP(G252,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="253" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H253" t="str">
         <f>IF(G253="","",VLOOKUP(G253,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="254" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="254" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H254" t="str">
         <f>IF(G254="","",VLOOKUP(G254,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="255" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H255" t="str">
         <f>IF(G255="","",VLOOKUP(G255,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="256" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H256" t="str">
         <f>IF(G256="","",VLOOKUP(G256,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="257" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="257" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H257" t="str">
         <f>IF(G257="","",VLOOKUP(G257,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="258" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="258" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H258" t="str">
         <f>IF(G258="","",VLOOKUP(G258,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="259" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="259" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H259" t="str">
         <f>IF(G259="","",VLOOKUP(G259,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="260" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H260" t="str">
         <f>IF(G260="","",VLOOKUP(G260,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="261" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="261" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H261" t="str">
         <f>IF(G261="","",VLOOKUP(G261,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="262" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H262" t="str">
         <f>IF(G262="","",VLOOKUP(G262,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="263" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="263" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H263" t="str">
         <f>IF(G263="","",VLOOKUP(G263,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="264" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="264" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H264" t="str">
         <f>IF(G264="","",VLOOKUP(G264,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="265" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="265" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H265" t="str">
         <f>IF(G265="","",VLOOKUP(G265,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="266" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="266" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H266" t="str">
         <f>IF(G266="","",VLOOKUP(G266,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="267" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="267" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H267" t="str">
         <f>IF(G267="","",VLOOKUP(G267,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="268" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="268" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H268" t="str">
         <f>IF(G268="","",VLOOKUP(G268,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="269" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="269" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H269" t="str">
         <f>IF(G269="","",VLOOKUP(G269,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="270" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="270" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H270" t="str">
         <f>IF(G270="","",VLOOKUP(G270,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="271" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="271" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H271" t="str">
         <f>IF(G271="","",VLOOKUP(G271,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="272" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="272" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H272" t="str">
         <f>IF(G272="","",VLOOKUP(G272,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="273" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="273" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H273" t="str">
         <f>IF(G273="","",VLOOKUP(G273,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="274" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="274" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H274" t="str">
         <f>IF(G274="","",VLOOKUP(G274,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="275" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="275" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H275" t="str">
         <f>IF(G275="","",VLOOKUP(G275,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="276" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="276" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H276" t="str">
         <f>IF(G276="","",VLOOKUP(G276,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="277" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="277" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H277" t="str">
         <f>IF(G277="","",VLOOKUP(G277,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="278" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="278" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H278" t="str">
         <f>IF(G278="","",VLOOKUP(G278,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="279" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="279" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H279" t="str">
         <f>IF(G279="","",VLOOKUP(G279,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="280" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="280" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H280" t="str">
         <f>IF(G280="","",VLOOKUP(G280,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="281" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="281" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H281" t="str">
         <f>IF(G281="","",VLOOKUP(G281,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="282" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="282" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H282" t="str">
         <f>IF(G282="","",VLOOKUP(G282,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="283" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="283" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H283" t="str">
         <f>IF(G283="","",VLOOKUP(G283,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="284" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="284" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H284" t="str">
         <f>IF(G284="","",VLOOKUP(G284,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="285" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="285" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H285" t="str">
         <f>IF(G285="","",VLOOKUP(G285,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="286" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="286" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H286" t="str">
         <f>IF(G286="","",VLOOKUP(G286,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="287" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="287" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H287" t="str">
         <f>IF(G287="","",VLOOKUP(G287,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="288" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="288" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H288" t="str">
         <f>IF(G288="","",VLOOKUP(G288,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="289" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="289" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H289" t="str">
         <f>IF(G289="","",VLOOKUP(G289,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="290" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="290" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H290" t="str">
         <f>IF(G290="","",VLOOKUP(G290,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="291" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="291" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H291" t="str">
         <f>IF(G291="","",VLOOKUP(G291,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="292" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="292" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H292" t="str">
         <f>IF(G292="","",VLOOKUP(G292,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="293" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="293" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H293" t="str">
         <f>IF(G293="","",VLOOKUP(G293,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="294" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="294" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H294" t="str">
         <f>IF(G294="","",VLOOKUP(G294,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="295" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="295" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H295" t="str">
         <f>IF(G295="","",VLOOKUP(G295,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="296" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="296" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H296" t="str">
         <f>IF(G296="","",VLOOKUP(G296,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="297" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="297" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H297" t="str">
         <f>IF(G297="","",VLOOKUP(G297,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="298" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="298" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H298" t="str">
         <f>IF(G298="","",VLOOKUP(G298,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="299" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="299" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H299" t="str">
         <f>IF(G299="","",VLOOKUP(G299,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="300" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="300" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H300" t="str">
         <f>IF(G300="","",VLOOKUP(G300,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="301" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="301" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H301" t="str">
         <f>IF(G301="","",VLOOKUP(G301,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="302" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="302" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H302" t="str">
         <f>IF(G302="","",VLOOKUP(G302,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="303" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="303" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H303" t="str">
         <f>IF(G303="","",VLOOKUP(G303,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="304" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="304" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H304" t="str">
         <f>IF(G304="","",VLOOKUP(G304,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="305" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="305" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H305" t="str">
         <f>IF(G305="","",VLOOKUP(G305,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="306" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="306" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H306" t="str">
         <f>IF(G306="","",VLOOKUP(G306,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="307" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="307" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H307" t="str">
         <f>IF(G307="","",VLOOKUP(G307,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="308" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="308" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H308" t="str">
         <f>IF(G308="","",VLOOKUP(G308,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="309" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="309" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H309" t="str">
         <f>IF(G309="","",VLOOKUP(G309,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="310" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="310" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H310" t="str">
         <f>IF(G310="","",VLOOKUP(G310,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="311" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="311" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H311" t="str">
         <f>IF(G311="","",VLOOKUP(G311,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="312" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="312" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H312" t="str">
         <f>IF(G312="","",VLOOKUP(G312,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="313" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="313" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H313" t="str">
         <f>IF(G313="","",VLOOKUP(G313,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="314" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="314" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H314" t="str">
         <f>IF(G314="","",VLOOKUP(G314,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="315" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="315" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H315" t="str">
         <f>IF(G315="","",VLOOKUP(G315,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="316" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="316" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H316" t="str">
         <f>IF(G316="","",VLOOKUP(G316,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="317" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="317" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H317" t="str">
         <f>IF(G317="","",VLOOKUP(G317,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="318" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="318" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H318" t="str">
         <f>IF(G318="","",VLOOKUP(G318,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="319" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="319" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H319" t="str">
         <f>IF(G319="","",VLOOKUP(G319,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="320" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="320" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H320" t="str">
         <f>IF(G320="","",VLOOKUP(G320,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="321" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="321" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H321" t="str">
         <f>IF(G321="","",VLOOKUP(G321,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="322" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="322" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H322" t="str">
         <f>IF(G322="","",VLOOKUP(G322,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="323" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="323" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H323" t="str">
         <f>IF(G323="","",VLOOKUP(G323,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="324" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="324" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H324" t="str">
         <f>IF(G324="","",VLOOKUP(G324,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="325" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="325" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H325" t="str">
         <f>IF(G325="","",VLOOKUP(G325,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="326" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="326" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H326" t="str">
         <f>IF(G326="","",VLOOKUP(G326,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="327" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="327" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H327" t="str">
         <f>IF(G327="","",VLOOKUP(G327,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="328" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="328" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H328" t="str">
         <f>IF(G328="","",VLOOKUP(G328,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="329" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="329" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H329" t="str">
         <f>IF(G329="","",VLOOKUP(G329,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="330" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="330" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H330" t="str">
         <f>IF(G330="","",VLOOKUP(G330,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="331" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="331" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H331" t="str">
         <f>IF(G331="","",VLOOKUP(G331,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="332" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="332" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H332" t="str">
         <f>IF(G332="","",VLOOKUP(G332,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="333" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="333" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H333" t="str">
         <f>IF(G333="","",VLOOKUP(G333,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="334" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="334" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H334" t="str">
         <f>IF(G334="","",VLOOKUP(G334,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="335" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="335" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H335" t="str">
         <f>IF(G335="","",VLOOKUP(G335,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="336" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="336" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H336" t="str">
         <f>IF(G336="","",VLOOKUP(G336,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="337" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="337" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H337" t="str">
         <f>IF(G337="","",VLOOKUP(G337,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="338" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="338" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H338" t="str">
         <f>IF(G338="","",VLOOKUP(G338,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="339" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="339" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H339" t="str">
         <f>IF(G339="","",VLOOKUP(G339,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="340" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="340" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H340" t="str">
         <f>IF(G340="","",VLOOKUP(G340,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="341" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="341" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H341" t="str">
         <f>IF(G341="","",VLOOKUP(G341,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="342" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="342" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H342" t="str">
         <f>IF(G342="","",VLOOKUP(G342,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="343" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="343" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H343" t="str">
         <f>IF(G343="","",VLOOKUP(G343,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="344" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="344" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H344" t="str">
         <f>IF(G344="","",VLOOKUP(G344,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="345" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="345" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H345" t="str">
         <f>IF(G345="","",VLOOKUP(G345,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="346" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="346" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H346" t="str">
         <f>IF(G346="","",VLOOKUP(G346,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="347" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="347" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H347" t="str">
         <f>IF(G347="","",VLOOKUP(G347,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="348" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="348" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H348" t="str">
         <f>IF(G348="","",VLOOKUP(G348,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="349" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="349" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H349" t="str">
         <f>IF(G349="","",VLOOKUP(G349,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="350" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="350" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H350" t="str">
         <f>IF(G350="","",VLOOKUP(G350,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="351" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="351" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H351" t="str">
         <f>IF(G351="","",VLOOKUP(G351,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="352" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="352" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H352" t="str">
         <f>IF(G352="","",VLOOKUP(G352,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="353" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="353" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H353" t="str">
         <f>IF(G353="","",VLOOKUP(G353,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="354" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="354" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H354" t="str">
         <f>IF(G354="","",VLOOKUP(G354,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="355" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="355" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H355" t="str">
         <f>IF(G355="","",VLOOKUP(G355,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="356" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="356" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H356" t="str">
         <f>IF(G356="","",VLOOKUP(G356,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="357" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="357" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H357" t="str">
         <f>IF(G357="","",VLOOKUP(G357,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="358" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="358" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H358" t="str">
         <f>IF(G358="","",VLOOKUP(G358,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="359" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="359" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H359" t="str">
         <f>IF(G359="","",VLOOKUP(G359,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="360" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="360" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H360" t="str">
         <f>IF(G360="","",VLOOKUP(G360,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="361" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="361" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H361" t="str">
         <f>IF(G361="","",VLOOKUP(G361,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="362" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="362" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H362" t="str">
         <f>IF(G362="","",VLOOKUP(G362,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="363" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="363" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H363" t="str">
         <f>IF(G363="","",VLOOKUP(G363,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="364" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="364" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H364" t="str">
         <f>IF(G364="","",VLOOKUP(G364,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="365" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="365" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H365" t="str">
         <f>IF(G365="","",VLOOKUP(G365,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="366" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="366" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H366" t="str">
         <f>IF(G366="","",VLOOKUP(G366,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="367" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="367" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H367" t="str">
         <f>IF(G367="","",VLOOKUP(G367,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="368" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="368" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H368" t="str">
         <f>IF(G368="","",VLOOKUP(G368,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="369" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="369" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H369" t="str">
         <f>IF(G369="","",VLOOKUP(G369,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="370" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="370" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H370" t="str">
         <f>IF(G370="","",VLOOKUP(G370,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="371" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="371" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H371" t="str">
         <f>IF(G371="","",VLOOKUP(G371,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="372" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="372" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H372" t="str">
         <f>IF(G372="","",VLOOKUP(G372,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="373" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="373" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H373" t="str">
         <f>IF(G373="","",VLOOKUP(G373,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="374" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="374" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H374" t="str">
         <f>IF(G374="","",VLOOKUP(G374,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="375" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="375" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H375" t="str">
         <f>IF(G375="","",VLOOKUP(G375,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="376" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="376" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H376" t="str">
         <f>IF(G376="","",VLOOKUP(G376,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="377" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="377" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H377" t="str">
         <f>IF(G377="","",VLOOKUP(G377,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="378" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="378" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H378" t="str">
         <f>IF(G378="","",VLOOKUP(G378,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="379" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="379" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H379" t="str">
         <f>IF(G379="","",VLOOKUP(G379,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="380" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="380" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H380" t="str">
         <f>IF(G380="","",VLOOKUP(G380,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="381" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="381" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H381" t="str">
         <f>IF(G381="","",VLOOKUP(G381,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="382" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="382" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H382" t="str">
         <f>IF(G382="","",VLOOKUP(G382,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="383" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="383" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H383" t="str">
         <f>IF(G383="","",VLOOKUP(G383,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="384" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="384" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H384" t="str">
         <f>IF(G384="","",VLOOKUP(G384,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="385" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="385" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H385" t="str">
         <f>IF(G385="","",VLOOKUP(G385,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="386" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="386" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H386" t="str">
         <f>IF(G386="","",VLOOKUP(G386,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="387" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="387" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H387" t="str">
         <f>IF(G387="","",VLOOKUP(G387,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="388" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="388" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H388" t="str">
         <f>IF(G388="","",VLOOKUP(G388,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="389" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="389" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H389" t="str">
         <f>IF(G389="","",VLOOKUP(G389,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="390" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="390" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H390" t="str">
         <f>IF(G390="","",VLOOKUP(G390,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="391" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="391" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H391" t="str">
         <f>IF(G391="","",VLOOKUP(G391,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="392" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="392" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H392" t="str">
         <f>IF(G392="","",VLOOKUP(G392,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="393" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="393" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H393" t="str">
         <f>IF(G393="","",VLOOKUP(G393,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="394" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="394" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H394" t="str">
         <f>IF(G394="","",VLOOKUP(G394,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="395" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="395" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H395" t="str">
         <f>IF(G395="","",VLOOKUP(G395,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="396" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="396" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H396" t="str">
         <f>IF(G396="","",VLOOKUP(G396,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="397" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="397" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H397" t="str">
         <f>IF(G397="","",VLOOKUP(G397,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="398" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="398" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H398" t="str">
         <f>IF(G398="","",VLOOKUP(G398,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="399" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="399" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H399" t="str">
         <f>IF(G399="","",VLOOKUP(G399,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="400" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="400" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H400" t="str">
         <f>IF(G400="","",VLOOKUP(G400,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="401" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="401" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H401" t="str">
         <f>IF(G401="","",VLOOKUP(G401,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="402" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="402" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H402" t="str">
         <f>IF(G402="","",VLOOKUP(G402,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="403" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="403" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H403" t="str">
         <f>IF(G403="","",VLOOKUP(G403,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="404" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="404" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H404" t="str">
         <f>IF(G404="","",VLOOKUP(G404,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="405" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="405" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H405" t="str">
         <f>IF(G405="","",VLOOKUP(G405,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="406" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="406" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H406" t="str">
         <f>IF(G406="","",VLOOKUP(G406,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="407" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="407" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H407" t="str">
         <f>IF(G407="","",VLOOKUP(G407,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="408" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="408" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H408" t="str">
         <f>IF(G408="","",VLOOKUP(G408,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="409" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="409" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H409" t="str">
         <f>IF(G409="","",VLOOKUP(G409,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="410" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="410" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H410" t="str">
         <f>IF(G410="","",VLOOKUP(G410,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="411" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="411" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H411" t="str">
         <f>IF(G411="","",VLOOKUP(G411,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="412" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="412" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H412" t="str">
         <f>IF(G412="","",VLOOKUP(G412,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="413" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="413" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H413" t="str">
         <f>IF(G413="","",VLOOKUP(G413,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="414" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="414" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H414" t="str">
         <f>IF(G414="","",VLOOKUP(G414,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="415" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="415" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H415" t="str">
         <f>IF(G415="","",VLOOKUP(G415,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="416" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="416" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H416" t="str">
         <f>IF(G416="","",VLOOKUP(G416,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="417" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="417" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H417" t="str">
         <f>IF(G417="","",VLOOKUP(G417,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="418" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="418" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H418" t="str">
         <f>IF(G418="","",VLOOKUP(G418,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="419" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="419" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H419" t="str">
         <f>IF(G419="","",VLOOKUP(G419,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="420" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="420" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H420" t="str">
         <f>IF(G420="","",VLOOKUP(G420,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="421" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="421" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H421" t="str">
         <f>IF(G421="","",VLOOKUP(G421,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="422" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="422" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H422" t="str">
         <f>IF(G422="","",VLOOKUP(G422,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="423" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="423" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H423" t="str">
         <f>IF(G423="","",VLOOKUP(G423,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="424" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="424" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H424" t="str">
         <f>IF(G424="","",VLOOKUP(G424,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="425" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="425" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H425" t="str">
         <f>IF(G425="","",VLOOKUP(G425,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="426" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="426" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H426" t="str">
         <f>IF(G426="","",VLOOKUP(G426,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="427" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="427" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H427" t="str">
         <f>IF(G427="","",VLOOKUP(G427,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="428" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="428" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H428" t="str">
         <f>IF(G428="","",VLOOKUP(G428,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="429" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="429" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H429" t="str">
         <f>IF(G429="","",VLOOKUP(G429,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="430" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="430" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H430" t="str">
         <f>IF(G430="","",VLOOKUP(G430,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="431" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="431" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H431" t="str">
         <f>IF(G431="","",VLOOKUP(G431,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="432" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="432" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H432" t="str">
         <f>IF(G432="","",VLOOKUP(G432,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="433" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="433" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H433" t="str">
         <f>IF(G433="","",VLOOKUP(G433,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="434" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="434" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H434" t="str">
         <f>IF(G434="","",VLOOKUP(G434,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="435" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="435" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H435" t="str">
         <f>IF(G435="","",VLOOKUP(G435,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="436" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="436" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H436" t="str">
         <f>IF(G436="","",VLOOKUP(G436,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="437" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="437" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H437" t="str">
         <f>IF(G437="","",VLOOKUP(G437,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="438" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="438" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H438" t="str">
         <f>IF(G438="","",VLOOKUP(G438,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="439" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="439" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H439" t="str">
         <f>IF(G439="","",VLOOKUP(G439,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="440" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="440" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H440" t="str">
         <f>IF(G440="","",VLOOKUP(G440,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="441" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="441" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H441" t="str">
         <f>IF(G441="","",VLOOKUP(G441,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="442" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="442" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H442" t="str">
         <f>IF(G442="","",VLOOKUP(G442,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="443" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="443" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H443" t="str">
         <f>IF(G443="","",VLOOKUP(G443,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="444" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="444" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H444" t="str">
         <f>IF(G444="","",VLOOKUP(G444,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="445" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="445" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H445" t="str">
         <f>IF(G445="","",VLOOKUP(G445,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="446" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="446" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H446" t="str">
         <f>IF(G446="","",VLOOKUP(G446,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="447" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="447" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H447" t="str">
         <f>IF(G447="","",VLOOKUP(G447,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="448" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="448" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H448" t="str">
         <f>IF(G448="","",VLOOKUP(G448,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="449" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="449" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H449" t="str">
         <f>IF(G449="","",VLOOKUP(G449,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="450" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="450" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H450" t="str">
         <f>IF(G450="","",VLOOKUP(G450,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="451" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="451" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H451" t="str">
         <f>IF(G451="","",VLOOKUP(G451,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="452" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="452" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H452" t="str">
         <f>IF(G452="","",VLOOKUP(G452,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="453" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="453" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H453" t="str">
         <f>IF(G453="","",VLOOKUP(G453,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="454" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="454" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H454" t="str">
         <f>IF(G454="","",VLOOKUP(G454,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="455" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="455" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H455" t="str">
         <f>IF(G455="","",VLOOKUP(G455,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="456" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="456" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H456" t="str">
         <f>IF(G456="","",VLOOKUP(G456,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="457" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="457" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H457" t="str">
         <f>IF(G457="","",VLOOKUP(G457,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="458" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="458" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H458" t="str">
         <f>IF(G458="","",VLOOKUP(G458,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="459" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="459" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H459" t="str">
         <f>IF(G459="","",VLOOKUP(G459,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="460" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="460" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H460" t="str">
         <f>IF(G460="","",VLOOKUP(G460,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="461" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="461" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H461" t="str">
         <f>IF(G461="","",VLOOKUP(G461,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="462" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="462" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H462" t="str">
         <f>IF(G462="","",VLOOKUP(G462,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="463" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="463" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H463" t="str">
         <f>IF(G463="","",VLOOKUP(G463,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="464" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="464" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H464" t="str">
         <f>IF(G464="","",VLOOKUP(G464,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="465" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="465" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H465" t="str">
         <f>IF(G465="","",VLOOKUP(G465,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="466" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="466" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H466" t="str">
         <f>IF(G466="","",VLOOKUP(G466,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="467" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="467" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H467" t="str">
         <f>IF(G467="","",VLOOKUP(G467,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="468" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="468" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H468" t="str">
         <f>IF(G468="","",VLOOKUP(G468,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="469" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="469" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H469" t="str">
         <f>IF(G469="","",VLOOKUP(G469,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="470" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="470" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H470" t="str">
         <f>IF(G470="","",VLOOKUP(G470,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="471" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="471" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H471" t="str">
         <f>IF(G471="","",VLOOKUP(G471,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="472" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="472" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H472" t="str">
         <f>IF(G472="","",VLOOKUP(G472,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="473" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="473" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H473" t="str">
         <f>IF(G473="","",VLOOKUP(G473,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="474" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="474" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H474" t="str">
         <f>IF(G474="","",VLOOKUP(G474,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="475" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="475" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H475" t="str">
         <f>IF(G475="","",VLOOKUP(G475,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="476" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="476" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H476" t="str">
         <f>IF(G476="","",VLOOKUP(G476,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="477" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="477" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H477" t="str">
         <f>IF(G477="","",VLOOKUP(G477,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="478" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="478" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H478" t="str">
         <f>IF(G478="","",VLOOKUP(G478,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="479" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="479" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H479" t="str">
         <f>IF(G479="","",VLOOKUP(G479,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="480" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="480" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H480" t="str">
         <f>IF(G480="","",VLOOKUP(G480,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="481" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="481" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H481" t="str">
         <f>IF(G481="","",VLOOKUP(G481,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="482" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="482" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H482" t="str">
         <f>IF(G482="","",VLOOKUP(G482,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="483" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="483" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H483" t="str">
         <f>IF(G483="","",VLOOKUP(G483,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="484" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="484" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H484" t="str">
         <f>IF(G484="","",VLOOKUP(G484,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="485" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="485" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H485" t="str">
         <f>IF(G485="","",VLOOKUP(G485,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="486" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="486" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H486" t="str">
         <f>IF(G486="","",VLOOKUP(G486,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="487" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="487" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H487" t="str">
         <f>IF(G487="","",VLOOKUP(G487,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="488" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="488" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H488" t="str">
         <f>IF(G488="","",VLOOKUP(G488,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="489" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="489" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H489" t="str">
         <f>IF(G489="","",VLOOKUP(G489,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="490" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="490" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H490" t="str">
         <f>IF(G490="","",VLOOKUP(G490,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="491" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="491" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H491" t="str">
         <f>IF(G491="","",VLOOKUP(G491,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="492" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="492" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H492" t="str">
         <f>IF(G492="","",VLOOKUP(G492,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="493" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="493" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H493" t="str">
         <f>IF(G493="","",VLOOKUP(G493,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="494" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="494" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H494" t="str">
         <f>IF(G494="","",VLOOKUP(G494,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="495" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="495" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H495" t="str">
         <f>IF(G495="","",VLOOKUP(G495,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="496" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="496" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H496" t="str">
         <f>IF(G496="","",VLOOKUP(G496,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="497" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="497" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H497" t="str">
         <f>IF(G497="","",VLOOKUP(G497,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="498" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="498" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H498" t="str">
         <f>IF(G498="","",VLOOKUP(G498,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="499" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="499" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H499" t="str">
         <f>IF(G499="","",VLOOKUP(G499,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="500" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="500" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H500" t="str">
         <f>IF(G500="","",VLOOKUP(G500,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
@@ -5560,7 +5581,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1">
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>REFERENCIA!$A$1:$A$15</xm:f>
           </x14:formula1>
@@ -5573,11 +5594,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.84375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -5585,7 +5606,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -5593,7 +5614,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -5601,7 +5622,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -5609,7 +5630,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -5617,7 +5638,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -5625,7 +5646,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -5633,7 +5654,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -5641,7 +5662,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -5649,7 +5670,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -5657,7 +5678,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -5665,7 +5686,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -5673,7 +5694,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -5681,7 +5702,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -5689,7 +5710,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>30</v>
       </c>
